--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -87,7 +87,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
-    <t>编号【KEY】</t>
+    <t>编号</t>
   </si>
   <si>
     <t>物品id</t>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="3">
         <v>4</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -349,12 +349,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1374,7 +1374,7 @@
         <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F6" s="3">
         <v>2000</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -349,12 +349,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1334,7 +1334,7 @@
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="F5" s="3">
         <v>2000</v>
@@ -1374,7 +1374,7 @@
         <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F6" s="3">
         <v>2000</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -349,12 +349,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1294,13 +1294,13 @@
         <v>24</v>
       </c>
       <c r="E4" s="3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F4" s="3">
         <v>2000</v>
       </c>
       <c r="G4" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H4" s="3">
         <v>1</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K4" s="3">
         <v>1</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -349,12 +349,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1454,7 +1454,7 @@
         <v>28</v>
       </c>
       <c r="E8" s="3">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
         <v>2000</v>
@@ -1469,10 +1469,10 @@
         <v>5</v>
       </c>
       <c r="J8" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="K8" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -1488,7 +1488,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>29</v>
@@ -1528,7 +1528,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -1494,7 +1494,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="3">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3">
         <v>4000</v>
@@ -1509,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="J9" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="K9" s="3">
         <v>1</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>编号</t>
   </si>
@@ -117,7 +117,10 @@
     <t>攻击范围</t>
   </si>
   <si>
-    <t>子弹数量</t>
+    <t>子弹数量(霰弹)</t>
+  </si>
+  <si>
+    <t>蓄力时间（狙击枪）</t>
   </si>
   <si>
     <t>id</t>
@@ -151,6 +154,9 @@
   </si>
   <si>
     <t>bulletNum</t>
+  </si>
+  <si>
+    <t>chargeTime</t>
   </si>
   <si>
     <t>string</t>
@@ -1170,8 +1176,8 @@
   <dimension ref="A1:P608"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="11" width="25.125" style="2" customWidth="1"/>
-    <col min="12" max="16" width="25.125" style="3" customWidth="1"/>
+    <col min="1" max="12" width="25.125" style="2" customWidth="1"/>
+    <col min="13" max="16" width="25.125" style="3" customWidth="1"/>
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1209,75 +1215,84 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" ht="16.5" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:16">
       <c r="A3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
@@ -1291,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>0.5</v>
@@ -1311,9 +1326,7 @@
       <c r="J4" s="3">
         <v>100</v>
       </c>
-      <c r="K4" s="3">
-        <v>1</v>
-      </c>
+      <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -1331,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3">
         <v>0.15</v>
@@ -1351,9 +1364,7 @@
       <c r="J5" s="3">
         <v>600</v>
       </c>
-      <c r="K5" s="3">
-        <v>1</v>
-      </c>
+      <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -1371,7 +1382,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
         <v>0.05</v>
@@ -1391,9 +1402,7 @@
       <c r="J6" s="3">
         <v>600</v>
       </c>
-      <c r="K6" s="3">
-        <v>1</v>
-      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -1411,7 +1420,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3">
         <v>0.2</v>
@@ -1431,9 +1440,7 @@
       <c r="J7" s="3">
         <v>600</v>
       </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
+      <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -1451,7 +1458,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E8" s="3">
         <v>1</v>
@@ -1491,7 +1498,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E9" s="3">
         <v>2</v>
@@ -1511,10 +1518,10 @@
       <c r="J9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
         <v>1</v>
       </c>
-      <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -1531,7 +1538,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E10" s="3">
         <v>0.2</v>
@@ -1551,9 +1558,7 @@
       <c r="J10" s="3">
         <v>600</v>
       </c>
-      <c r="K10" s="3">
-        <v>1</v>
-      </c>
+      <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -1662,8 +1667,9 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1675,8 +1681,9 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1688,8 +1695,9 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1701,8 +1709,9 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1714,8 +1723,9 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1727,8 +1737,9 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1740,8 +1751,9 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" s="5"/>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1753,8 +1765,9 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1766,8 +1779,9 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1779,8 +1793,9 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25" s="5"/>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1792,8 +1807,9 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1805,8 +1821,9 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27" s="5"/>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1818,8 +1835,9 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28" s="5"/>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1831,8 +1849,9 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29" s="5"/>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1844,8 +1863,9 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30" s="5"/>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -1857,8 +1877,9 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31" s="5"/>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -1870,8 +1891,9 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32" s="5"/>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -1883,8 +1905,9 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33" s="5"/>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -1896,8 +1919,9 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -1909,8 +1933,9 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -1922,8 +1947,9 @@
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36" s="5"/>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -1935,8 +1961,9 @@
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -1948,8 +1975,9 @@
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="L38" s="5"/>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -1961,8 +1989,9 @@
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -1974,8 +2003,9 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -1987,8 +2017,9 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2000,8 +2031,9 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2013,8 +2045,9 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2026,8 +2059,9 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2039,8 +2073,9 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2052,8 +2087,9 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2065,8 +2101,9 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2078,8 +2115,9 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2091,8 +2129,9 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2104,8 +2143,9 @@
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2117,8 +2157,9 @@
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2130,8 +2171,9 @@
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2143,8 +2185,9 @@
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2156,8 +2199,9 @@
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2169,8 +2213,9 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2182,8 +2227,9 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2195,8 +2241,9 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2208,8 +2255,9 @@
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="L58" s="5"/>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2221,8 +2269,9 @@
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="L59" s="5"/>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2234,8 +2283,9 @@
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="L60" s="5"/>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2247,8 +2297,9 @@
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="L61" s="5"/>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2260,8 +2311,9 @@
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
-    </row>
-    <row r="63" spans="1:11">
+      <c r="L62" s="5"/>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2273,8 +2325,9 @@
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="L63" s="5"/>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2286,8 +2339,9 @@
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="L64" s="5"/>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2299,8 +2353,9 @@
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
-    </row>
-    <row r="66" spans="1:11">
+      <c r="L65" s="5"/>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -2312,8 +2367,9 @@
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="L66" s="5"/>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2325,8 +2381,9 @@
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="L67" s="5"/>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -2338,8 +2395,9 @@
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
-    </row>
-    <row r="69" spans="1:11">
+      <c r="L68" s="5"/>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2351,8 +2409,9 @@
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="L69" s="5"/>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -2364,8 +2423,9 @@
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="L70" s="5"/>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -2377,8 +2437,9 @@
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="L71" s="5"/>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -2390,8 +2451,9 @@
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
-    </row>
-    <row r="73" spans="1:11">
+      <c r="L72" s="5"/>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -2403,8 +2465,9 @@
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
-    </row>
-    <row r="74" spans="1:11">
+      <c r="L73" s="5"/>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -2416,8 +2479,9 @@
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
-    </row>
-    <row r="75" spans="1:11">
+      <c r="L74" s="5"/>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -2429,8 +2493,9 @@
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
-    </row>
-    <row r="76" spans="1:11">
+      <c r="L75" s="5"/>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -2442,8 +2507,9 @@
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
-    </row>
-    <row r="77" spans="1:11">
+      <c r="L76" s="5"/>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -2455,8 +2521,9 @@
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
-    </row>
-    <row r="78" spans="1:11">
+      <c r="L77" s="5"/>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -2468,8 +2535,9 @@
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
-    </row>
-    <row r="79" spans="1:11">
+      <c r="L78" s="5"/>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -2481,8 +2549,9 @@
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
-    </row>
-    <row r="80" spans="1:11">
+      <c r="L79" s="5"/>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -2494,8 +2563,9 @@
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
-    </row>
-    <row r="81" spans="1:11">
+      <c r="L80" s="5"/>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -2507,8 +2577,9 @@
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
-    </row>
-    <row r="82" spans="1:11">
+      <c r="L81" s="5"/>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -2520,8 +2591,9 @@
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
-    </row>
-    <row r="83" spans="1:11">
+      <c r="L82" s="5"/>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -2533,8 +2605,9 @@
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
-    </row>
-    <row r="84" spans="1:11">
+      <c r="L83" s="5"/>
+    </row>
+    <row r="84" spans="1:12">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -2546,8 +2619,9 @@
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
       <c r="K84" s="5"/>
-    </row>
-    <row r="85" spans="1:11">
+      <c r="L84" s="5"/>
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -2559,8 +2633,9 @@
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
       <c r="K85" s="5"/>
-    </row>
-    <row r="86" spans="1:11">
+      <c r="L85" s="5"/>
+    </row>
+    <row r="86" spans="1:12">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -2572,8 +2647,9 @@
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="5"/>
-    </row>
-    <row r="87" spans="1:11">
+      <c r="L86" s="5"/>
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -2585,8 +2661,9 @@
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="5"/>
-    </row>
-    <row r="88" spans="1:11">
+      <c r="L87" s="5"/>
+    </row>
+    <row r="88" spans="1:12">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -2598,8 +2675,9 @@
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
       <c r="K88" s="5"/>
-    </row>
-    <row r="89" spans="1:11">
+      <c r="L88" s="5"/>
+    </row>
+    <row r="89" spans="1:12">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -2611,8 +2689,9 @@
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="5"/>
-    </row>
-    <row r="90" spans="1:11">
+      <c r="L89" s="5"/>
+    </row>
+    <row r="90" spans="1:12">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -2624,8 +2703,9 @@
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
-    </row>
-    <row r="91" spans="1:11">
+      <c r="L90" s="5"/>
+    </row>
+    <row r="91" spans="1:12">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -2637,8 +2717,9 @@
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
       <c r="K91" s="5"/>
-    </row>
-    <row r="92" spans="1:11">
+      <c r="L91" s="5"/>
+    </row>
+    <row r="92" spans="1:12">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -2650,8 +2731,9 @@
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
       <c r="K92" s="5"/>
-    </row>
-    <row r="93" spans="1:11">
+      <c r="L92" s="5"/>
+    </row>
+    <row r="93" spans="1:12">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -2663,8 +2745,9 @@
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
-    </row>
-    <row r="94" spans="1:11">
+      <c r="L93" s="5"/>
+    </row>
+    <row r="94" spans="1:12">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -2676,8 +2759,9 @@
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
-    </row>
-    <row r="95" spans="1:11">
+      <c r="L94" s="5"/>
+    </row>
+    <row r="95" spans="1:12">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -2689,8 +2773,9 @@
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
       <c r="K95" s="5"/>
-    </row>
-    <row r="96" spans="1:11">
+      <c r="L95" s="5"/>
+    </row>
+    <row r="96" spans="1:12">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -2702,8 +2787,9 @@
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
       <c r="K96" s="5"/>
-    </row>
-    <row r="97" spans="1:11">
+      <c r="L96" s="5"/>
+    </row>
+    <row r="97" spans="1:12">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -2715,8 +2801,9 @@
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
-    </row>
-    <row r="98" spans="1:11">
+      <c r="L97" s="5"/>
+    </row>
+    <row r="98" spans="1:12">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -2728,8 +2815,9 @@
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="5"/>
-    </row>
-    <row r="99" spans="1:11">
+      <c r="L98" s="5"/>
+    </row>
+    <row r="99" spans="1:12">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -2741,8 +2829,9 @@
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
-    </row>
-    <row r="100" spans="1:11">
+      <c r="L99" s="5"/>
+    </row>
+    <row r="100" spans="1:12">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -2754,8 +2843,9 @@
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="5"/>
-    </row>
-    <row r="101" spans="1:11">
+      <c r="L100" s="5"/>
+    </row>
+    <row r="101" spans="1:12">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -2767,8 +2857,9 @@
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
-    </row>
-    <row r="102" spans="1:11">
+      <c r="L101" s="5"/>
+    </row>
+    <row r="102" spans="1:12">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -2780,8 +2871,9 @@
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
-    </row>
-    <row r="103" spans="1:11">
+      <c r="L102" s="5"/>
+    </row>
+    <row r="103" spans="1:12">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -2793,8 +2885,9 @@
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="5"/>
-    </row>
-    <row r="104" spans="1:11">
+      <c r="L103" s="5"/>
+    </row>
+    <row r="104" spans="1:12">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -2806,8 +2899,9 @@
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
-    </row>
-    <row r="105" spans="1:11">
+      <c r="L104" s="5"/>
+    </row>
+    <row r="105" spans="1:12">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -2819,8 +2913,9 @@
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
-    </row>
-    <row r="106" spans="1:11">
+      <c r="L105" s="5"/>
+    </row>
+    <row r="106" spans="1:12">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -2832,8 +2927,9 @@
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="5"/>
-    </row>
-    <row r="107" spans="1:11">
+      <c r="L106" s="5"/>
+    </row>
+    <row r="107" spans="1:12">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -2845,8 +2941,9 @@
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
-    </row>
-    <row r="108" spans="1:11">
+      <c r="L107" s="5"/>
+    </row>
+    <row r="108" spans="1:12">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -2858,8 +2955,9 @@
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
-    </row>
-    <row r="109" spans="1:11">
+      <c r="L108" s="5"/>
+    </row>
+    <row r="109" spans="1:12">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -2871,8 +2969,9 @@
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
-    </row>
-    <row r="110" spans="1:11">
+      <c r="L109" s="5"/>
+    </row>
+    <row r="110" spans="1:12">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -2884,8 +2983,9 @@
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
       <c r="K110" s="5"/>
-    </row>
-    <row r="111" spans="1:11">
+      <c r="L110" s="5"/>
+    </row>
+    <row r="111" spans="1:12">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -2897,8 +2997,9 @@
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="5"/>
-    </row>
-    <row r="112" spans="1:11">
+      <c r="L111" s="5"/>
+    </row>
+    <row r="112" spans="1:12">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -2910,8 +3011,9 @@
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5"/>
-    </row>
-    <row r="113" spans="1:11">
+      <c r="L112" s="5"/>
+    </row>
+    <row r="113" spans="1:12">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -2923,8 +3025,9 @@
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
-    </row>
-    <row r="114" spans="1:11">
+      <c r="L113" s="5"/>
+    </row>
+    <row r="114" spans="1:12">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -2936,8 +3039,9 @@
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5"/>
-    </row>
-    <row r="115" spans="1:11">
+      <c r="L114" s="5"/>
+    </row>
+    <row r="115" spans="1:12">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -2949,8 +3053,9 @@
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
       <c r="K115" s="5"/>
-    </row>
-    <row r="116" spans="1:11">
+      <c r="L115" s="5"/>
+    </row>
+    <row r="116" spans="1:12">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -2962,8 +3067,9 @@
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
       <c r="K116" s="5"/>
-    </row>
-    <row r="117" spans="1:11">
+      <c r="L116" s="5"/>
+    </row>
+    <row r="117" spans="1:12">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -2975,8 +3081,9 @@
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
       <c r="K117" s="5"/>
-    </row>
-    <row r="118" spans="1:11">
+      <c r="L117" s="5"/>
+    </row>
+    <row r="118" spans="1:12">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -2988,8 +3095,9 @@
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="5"/>
-    </row>
-    <row r="119" spans="1:11">
+      <c r="L118" s="5"/>
+    </row>
+    <row r="119" spans="1:12">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -3001,8 +3109,9 @@
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
       <c r="K119" s="5"/>
-    </row>
-    <row r="120" spans="1:11">
+      <c r="L119" s="5"/>
+    </row>
+    <row r="120" spans="1:12">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -3014,8 +3123,9 @@
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
       <c r="K120" s="5"/>
-    </row>
-    <row r="121" spans="1:11">
+      <c r="L120" s="5"/>
+    </row>
+    <row r="121" spans="1:12">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -3027,8 +3137,9 @@
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
       <c r="K121" s="5"/>
-    </row>
-    <row r="122" spans="1:11">
+      <c r="L121" s="5"/>
+    </row>
+    <row r="122" spans="1:12">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -3040,8 +3151,9 @@
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="5"/>
-    </row>
-    <row r="123" spans="1:11">
+      <c r="L122" s="5"/>
+    </row>
+    <row r="123" spans="1:12">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -3053,8 +3165,9 @@
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
       <c r="K123" s="5"/>
-    </row>
-    <row r="124" spans="1:11">
+      <c r="L123" s="5"/>
+    </row>
+    <row r="124" spans="1:12">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -3066,8 +3179,9 @@
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="5"/>
-    </row>
-    <row r="125" spans="1:11">
+      <c r="L124" s="5"/>
+    </row>
+    <row r="125" spans="1:12">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -3079,8 +3193,9 @@
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
-    </row>
-    <row r="126" spans="1:11">
+      <c r="L125" s="5"/>
+    </row>
+    <row r="126" spans="1:12">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -3092,8 +3207,9 @@
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
-    </row>
-    <row r="127" spans="1:11">
+      <c r="L126" s="5"/>
+    </row>
+    <row r="127" spans="1:12">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -3105,8 +3221,9 @@
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="5"/>
-    </row>
-    <row r="128" spans="1:11">
+      <c r="L127" s="5"/>
+    </row>
+    <row r="128" spans="1:12">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -3118,8 +3235,9 @@
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="5"/>
-    </row>
-    <row r="129" spans="1:11">
+      <c r="L128" s="5"/>
+    </row>
+    <row r="129" spans="1:12">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -3131,8 +3249,9 @@
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
-    </row>
-    <row r="130" spans="1:11">
+      <c r="L129" s="5"/>
+    </row>
+    <row r="130" spans="1:12">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -3144,8 +3263,9 @@
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
-    </row>
-    <row r="131" spans="1:11">
+      <c r="L130" s="5"/>
+    </row>
+    <row r="131" spans="1:12">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -3157,8 +3277,9 @@
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5"/>
-    </row>
-    <row r="132" spans="1:11">
+      <c r="L131" s="5"/>
+    </row>
+    <row r="132" spans="1:12">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -3170,8 +3291,9 @@
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5"/>
-    </row>
-    <row r="133" spans="1:11">
+      <c r="L132" s="5"/>
+    </row>
+    <row r="133" spans="1:12">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -3183,8 +3305,9 @@
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5"/>
-    </row>
-    <row r="134" spans="1:11">
+      <c r="L133" s="5"/>
+    </row>
+    <row r="134" spans="1:12">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -3196,8 +3319,9 @@
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="5"/>
-    </row>
-    <row r="135" spans="1:11">
+      <c r="L134" s="5"/>
+    </row>
+    <row r="135" spans="1:12">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -3209,8 +3333,9 @@
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
-    </row>
-    <row r="136" spans="1:11">
+      <c r="L135" s="5"/>
+    </row>
+    <row r="136" spans="1:12">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -3222,8 +3347,9 @@
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="5"/>
-    </row>
-    <row r="137" spans="1:11">
+      <c r="L136" s="5"/>
+    </row>
+    <row r="137" spans="1:12">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -3235,8 +3361,9 @@
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
       <c r="K137" s="5"/>
-    </row>
-    <row r="138" spans="1:11">
+      <c r="L137" s="5"/>
+    </row>
+    <row r="138" spans="1:12">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -3248,8 +3375,9 @@
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
-    </row>
-    <row r="139" spans="1:11">
+      <c r="L138" s="5"/>
+    </row>
+    <row r="139" spans="1:12">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -3261,8 +3389,9 @@
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5"/>
-    </row>
-    <row r="140" spans="1:11">
+      <c r="L139" s="5"/>
+    </row>
+    <row r="140" spans="1:12">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -3274,8 +3403,9 @@
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
       <c r="K140" s="5"/>
-    </row>
-    <row r="141" spans="1:11">
+      <c r="L140" s="5"/>
+    </row>
+    <row r="141" spans="1:12">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -3287,8 +3417,9 @@
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
       <c r="K141" s="5"/>
-    </row>
-    <row r="142" spans="1:11">
+      <c r="L141" s="5"/>
+    </row>
+    <row r="142" spans="1:12">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -3300,8 +3431,9 @@
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
       <c r="K142" s="5"/>
-    </row>
-    <row r="143" spans="1:11">
+      <c r="L142" s="5"/>
+    </row>
+    <row r="143" spans="1:12">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -3313,8 +3445,9 @@
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
       <c r="K143" s="5"/>
-    </row>
-    <row r="144" spans="1:11">
+      <c r="L143" s="5"/>
+    </row>
+    <row r="144" spans="1:12">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -3326,8 +3459,9 @@
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
       <c r="K144" s="5"/>
-    </row>
-    <row r="145" spans="1:11">
+      <c r="L144" s="5"/>
+    </row>
+    <row r="145" spans="1:12">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -3339,8 +3473,9 @@
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
-    </row>
-    <row r="146" spans="1:11">
+      <c r="L145" s="5"/>
+    </row>
+    <row r="146" spans="1:12">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -3352,8 +3487,9 @@
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
-    </row>
-    <row r="147" spans="1:11">
+      <c r="L146" s="5"/>
+    </row>
+    <row r="147" spans="1:12">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -3365,8 +3501,9 @@
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
-    </row>
-    <row r="148" spans="1:11">
+      <c r="L147" s="5"/>
+    </row>
+    <row r="148" spans="1:12">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -3378,8 +3515,9 @@
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
-    </row>
-    <row r="149" spans="1:11">
+      <c r="L148" s="5"/>
+    </row>
+    <row r="149" spans="1:12">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -3391,8 +3529,9 @@
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
-    </row>
-    <row r="150" spans="1:11">
+      <c r="L149" s="5"/>
+    </row>
+    <row r="150" spans="1:12">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -3404,8 +3543,9 @@
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
-    </row>
-    <row r="151" spans="1:11">
+      <c r="L150" s="5"/>
+    </row>
+    <row r="151" spans="1:12">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -3417,8 +3557,9 @@
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
-    </row>
-    <row r="152" spans="1:11">
+      <c r="L151" s="5"/>
+    </row>
+    <row r="152" spans="1:12">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -3430,8 +3571,9 @@
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
-    </row>
-    <row r="153" spans="1:11">
+      <c r="L152" s="5"/>
+    </row>
+    <row r="153" spans="1:12">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -3443,8 +3585,9 @@
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
-    </row>
-    <row r="154" spans="1:11">
+      <c r="L153" s="5"/>
+    </row>
+    <row r="154" spans="1:12">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -3456,8 +3599,9 @@
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
-    </row>
-    <row r="155" spans="1:11">
+      <c r="L154" s="5"/>
+    </row>
+    <row r="155" spans="1:12">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -3469,8 +3613,9 @@
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
-    </row>
-    <row r="156" spans="1:11">
+      <c r="L155" s="5"/>
+    </row>
+    <row r="156" spans="1:12">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -3482,8 +3627,9 @@
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
-    </row>
-    <row r="157" spans="1:11">
+      <c r="L156" s="5"/>
+    </row>
+    <row r="157" spans="1:12">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -3495,8 +3641,9 @@
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
-    </row>
-    <row r="158" spans="1:11">
+      <c r="L157" s="5"/>
+    </row>
+    <row r="158" spans="1:12">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -3508,8 +3655,9 @@
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
-    </row>
-    <row r="159" spans="1:11">
+      <c r="L158" s="5"/>
+    </row>
+    <row r="159" spans="1:12">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -3521,8 +3669,9 @@
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
-    </row>
-    <row r="160" spans="1:11">
+      <c r="L159" s="5"/>
+    </row>
+    <row r="160" spans="1:12">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -3534,8 +3683,9 @@
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
-    </row>
-    <row r="161" spans="1:11">
+      <c r="L160" s="5"/>
+    </row>
+    <row r="161" spans="1:12">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -3547,8 +3697,9 @@
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
-    </row>
-    <row r="162" spans="1:11">
+      <c r="L161" s="5"/>
+    </row>
+    <row r="162" spans="1:12">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -3560,8 +3711,9 @@
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
       <c r="K162" s="5"/>
-    </row>
-    <row r="163" spans="1:11">
+      <c r="L162" s="5"/>
+    </row>
+    <row r="163" spans="1:12">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -3573,8 +3725,9 @@
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
       <c r="K163" s="5"/>
-    </row>
-    <row r="164" spans="1:11">
+      <c r="L163" s="5"/>
+    </row>
+    <row r="164" spans="1:12">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -3586,8 +3739,9 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5"/>
-    </row>
-    <row r="165" spans="1:11">
+      <c r="L164" s="5"/>
+    </row>
+    <row r="165" spans="1:12">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -3599,8 +3753,9 @@
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
       <c r="K165" s="5"/>
-    </row>
-    <row r="166" spans="1:11">
+      <c r="L165" s="5"/>
+    </row>
+    <row r="166" spans="1:12">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -3612,8 +3767,9 @@
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
       <c r="K166" s="5"/>
-    </row>
-    <row r="167" spans="1:11">
+      <c r="L166" s="5"/>
+    </row>
+    <row r="167" spans="1:12">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -3625,8 +3781,9 @@
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
-    </row>
-    <row r="168" spans="1:11">
+      <c r="L167" s="5"/>
+    </row>
+    <row r="168" spans="1:12">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -3638,8 +3795,9 @@
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
       <c r="K168" s="5"/>
-    </row>
-    <row r="169" spans="1:11">
+      <c r="L168" s="5"/>
+    </row>
+    <row r="169" spans="1:12">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -3651,8 +3809,9 @@
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
       <c r="K169" s="5"/>
-    </row>
-    <row r="170" spans="1:11">
+      <c r="L169" s="5"/>
+    </row>
+    <row r="170" spans="1:12">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -3664,8 +3823,9 @@
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
       <c r="K170" s="5"/>
-    </row>
-    <row r="171" spans="1:11">
+      <c r="L170" s="5"/>
+    </row>
+    <row r="171" spans="1:12">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -3677,8 +3837,9 @@
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
       <c r="K171" s="5"/>
-    </row>
-    <row r="172" spans="1:11">
+      <c r="L171" s="5"/>
+    </row>
+    <row r="172" spans="1:12">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -3690,8 +3851,9 @@
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
       <c r="K172" s="5"/>
-    </row>
-    <row r="173" spans="1:11">
+      <c r="L172" s="5"/>
+    </row>
+    <row r="173" spans="1:12">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -3703,8 +3865,9 @@
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="5"/>
-    </row>
-    <row r="174" spans="1:11">
+      <c r="L173" s="5"/>
+    </row>
+    <row r="174" spans="1:12">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -3716,8 +3879,9 @@
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
       <c r="K174" s="5"/>
-    </row>
-    <row r="175" spans="1:11">
+      <c r="L174" s="5"/>
+    </row>
+    <row r="175" spans="1:12">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -3729,8 +3893,9 @@
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
       <c r="K175" s="5"/>
-    </row>
-    <row r="176" spans="1:11">
+      <c r="L175" s="5"/>
+    </row>
+    <row r="176" spans="1:12">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -3742,8 +3907,9 @@
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
       <c r="K176" s="5"/>
-    </row>
-    <row r="177" spans="1:11">
+      <c r="L176" s="5"/>
+    </row>
+    <row r="177" spans="1:12">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -3755,8 +3921,9 @@
       <c r="I177" s="5"/>
       <c r="J177" s="5"/>
       <c r="K177" s="5"/>
-    </row>
-    <row r="178" spans="1:11">
+      <c r="L177" s="5"/>
+    </row>
+    <row r="178" spans="1:12">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -3768,8 +3935,9 @@
       <c r="I178" s="5"/>
       <c r="J178" s="5"/>
       <c r="K178" s="5"/>
-    </row>
-    <row r="179" spans="1:11">
+      <c r="L178" s="5"/>
+    </row>
+    <row r="179" spans="1:12">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -3781,8 +3949,9 @@
       <c r="I179" s="5"/>
       <c r="J179" s="5"/>
       <c r="K179" s="5"/>
-    </row>
-    <row r="180" spans="1:11">
+      <c r="L179" s="5"/>
+    </row>
+    <row r="180" spans="1:12">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -3794,8 +3963,9 @@
       <c r="I180" s="5"/>
       <c r="J180" s="5"/>
       <c r="K180" s="5"/>
-    </row>
-    <row r="181" spans="1:11">
+      <c r="L180" s="5"/>
+    </row>
+    <row r="181" spans="1:12">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -3807,8 +3977,9 @@
       <c r="I181" s="5"/>
       <c r="J181" s="5"/>
       <c r="K181" s="5"/>
-    </row>
-    <row r="182" spans="1:11">
+      <c r="L181" s="5"/>
+    </row>
+    <row r="182" spans="1:12">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -3820,8 +3991,9 @@
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
       <c r="K182" s="5"/>
-    </row>
-    <row r="183" spans="1:11">
+      <c r="L182" s="5"/>
+    </row>
+    <row r="183" spans="1:12">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -3833,8 +4005,9 @@
       <c r="I183" s="5"/>
       <c r="J183" s="5"/>
       <c r="K183" s="5"/>
-    </row>
-    <row r="184" spans="1:11">
+      <c r="L183" s="5"/>
+    </row>
+    <row r="184" spans="1:12">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -3846,8 +4019,9 @@
       <c r="I184" s="5"/>
       <c r="J184" s="5"/>
       <c r="K184" s="5"/>
-    </row>
-    <row r="185" spans="1:11">
+      <c r="L184" s="5"/>
+    </row>
+    <row r="185" spans="1:12">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -3859,8 +4033,9 @@
       <c r="I185" s="5"/>
       <c r="J185" s="5"/>
       <c r="K185" s="5"/>
-    </row>
-    <row r="186" spans="1:11">
+      <c r="L185" s="5"/>
+    </row>
+    <row r="186" spans="1:12">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -3872,8 +4047,9 @@
       <c r="I186" s="5"/>
       <c r="J186" s="5"/>
       <c r="K186" s="5"/>
-    </row>
-    <row r="187" spans="1:11">
+      <c r="L186" s="5"/>
+    </row>
+    <row r="187" spans="1:12">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -3885,8 +4061,9 @@
       <c r="I187" s="5"/>
       <c r="J187" s="5"/>
       <c r="K187" s="5"/>
-    </row>
-    <row r="188" spans="1:11">
+      <c r="L187" s="5"/>
+    </row>
+    <row r="188" spans="1:12">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -3898,8 +4075,9 @@
       <c r="I188" s="5"/>
       <c r="J188" s="5"/>
       <c r="K188" s="5"/>
-    </row>
-    <row r="189" spans="1:11">
+      <c r="L188" s="5"/>
+    </row>
+    <row r="189" spans="1:12">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -3911,8 +4089,9 @@
       <c r="I189" s="5"/>
       <c r="J189" s="5"/>
       <c r="K189" s="5"/>
-    </row>
-    <row r="190" spans="1:11">
+      <c r="L189" s="5"/>
+    </row>
+    <row r="190" spans="1:12">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -3924,8 +4103,9 @@
       <c r="I190" s="5"/>
       <c r="J190" s="5"/>
       <c r="K190" s="5"/>
-    </row>
-    <row r="191" spans="1:11">
+      <c r="L190" s="5"/>
+    </row>
+    <row r="191" spans="1:12">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -3937,8 +4117,9 @@
       <c r="I191" s="5"/>
       <c r="J191" s="5"/>
       <c r="K191" s="5"/>
-    </row>
-    <row r="192" spans="1:11">
+      <c r="L191" s="5"/>
+    </row>
+    <row r="192" spans="1:12">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -3950,8 +4131,9 @@
       <c r="I192" s="5"/>
       <c r="J192" s="5"/>
       <c r="K192" s="5"/>
-    </row>
-    <row r="193" spans="1:11">
+      <c r="L192" s="5"/>
+    </row>
+    <row r="193" spans="1:12">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -3963,8 +4145,9 @@
       <c r="I193" s="5"/>
       <c r="J193" s="5"/>
       <c r="K193" s="5"/>
-    </row>
-    <row r="194" spans="1:11">
+      <c r="L193" s="5"/>
+    </row>
+    <row r="194" spans="1:12">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -3976,8 +4159,9 @@
       <c r="I194" s="5"/>
       <c r="J194" s="5"/>
       <c r="K194" s="5"/>
-    </row>
-    <row r="195" spans="1:11">
+      <c r="L194" s="5"/>
+    </row>
+    <row r="195" spans="1:12">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -3989,8 +4173,9 @@
       <c r="I195" s="5"/>
       <c r="J195" s="5"/>
       <c r="K195" s="5"/>
-    </row>
-    <row r="196" spans="1:11">
+      <c r="L195" s="5"/>
+    </row>
+    <row r="196" spans="1:12">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -4002,8 +4187,9 @@
       <c r="I196" s="5"/>
       <c r="J196" s="5"/>
       <c r="K196" s="5"/>
-    </row>
-    <row r="197" spans="1:11">
+      <c r="L196" s="5"/>
+    </row>
+    <row r="197" spans="1:12">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -4015,8 +4201,9 @@
       <c r="I197" s="5"/>
       <c r="J197" s="5"/>
       <c r="K197" s="5"/>
-    </row>
-    <row r="198" spans="1:11">
+      <c r="L197" s="5"/>
+    </row>
+    <row r="198" spans="1:12">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -4028,8 +4215,9 @@
       <c r="I198" s="5"/>
       <c r="J198" s="5"/>
       <c r="K198" s="5"/>
-    </row>
-    <row r="199" spans="1:11">
+      <c r="L198" s="5"/>
+    </row>
+    <row r="199" spans="1:12">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -4041,8 +4229,9 @@
       <c r="I199" s="5"/>
       <c r="J199" s="5"/>
       <c r="K199" s="5"/>
-    </row>
-    <row r="200" spans="1:11">
+      <c r="L199" s="5"/>
+    </row>
+    <row r="200" spans="1:12">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -4054,8 +4243,9 @@
       <c r="I200" s="5"/>
       <c r="J200" s="5"/>
       <c r="K200" s="5"/>
-    </row>
-    <row r="201" spans="1:11">
+      <c r="L200" s="5"/>
+    </row>
+    <row r="201" spans="1:12">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -4067,8 +4257,9 @@
       <c r="I201" s="5"/>
       <c r="J201" s="5"/>
       <c r="K201" s="5"/>
-    </row>
-    <row r="202" spans="1:11">
+      <c r="L201" s="5"/>
+    </row>
+    <row r="202" spans="1:12">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -4080,8 +4271,9 @@
       <c r="I202" s="5"/>
       <c r="J202" s="5"/>
       <c r="K202" s="5"/>
-    </row>
-    <row r="203" spans="1:11">
+      <c r="L202" s="5"/>
+    </row>
+    <row r="203" spans="1:12">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -4093,8 +4285,9 @@
       <c r="I203" s="5"/>
       <c r="J203" s="5"/>
       <c r="K203" s="5"/>
-    </row>
-    <row r="204" spans="1:11">
+      <c r="L203" s="5"/>
+    </row>
+    <row r="204" spans="1:12">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -4106,8 +4299,9 @@
       <c r="I204" s="5"/>
       <c r="J204" s="5"/>
       <c r="K204" s="5"/>
-    </row>
-    <row r="205" spans="1:11">
+      <c r="L204" s="5"/>
+    </row>
+    <row r="205" spans="1:12">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -4119,8 +4313,9 @@
       <c r="I205" s="5"/>
       <c r="J205" s="5"/>
       <c r="K205" s="5"/>
-    </row>
-    <row r="206" spans="1:11">
+      <c r="L205" s="5"/>
+    </row>
+    <row r="206" spans="1:12">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -4132,8 +4327,9 @@
       <c r="I206" s="5"/>
       <c r="J206" s="5"/>
       <c r="K206" s="5"/>
-    </row>
-    <row r="207" spans="1:11">
+      <c r="L206" s="5"/>
+    </row>
+    <row r="207" spans="1:12">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -4145,8 +4341,9 @@
       <c r="I207" s="5"/>
       <c r="J207" s="5"/>
       <c r="K207" s="5"/>
-    </row>
-    <row r="208" spans="1:11">
+      <c r="L207" s="5"/>
+    </row>
+    <row r="208" spans="1:12">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -4158,8 +4355,9 @@
       <c r="I208" s="5"/>
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
-    </row>
-    <row r="209" spans="1:11">
+      <c r="L208" s="5"/>
+    </row>
+    <row r="209" spans="1:12">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -4171,8 +4369,9 @@
       <c r="I209" s="5"/>
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
-    </row>
-    <row r="210" spans="1:11">
+      <c r="L209" s="5"/>
+    </row>
+    <row r="210" spans="1:12">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -4184,8 +4383,9 @@
       <c r="I210" s="5"/>
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
-    </row>
-    <row r="211" spans="1:11">
+      <c r="L210" s="5"/>
+    </row>
+    <row r="211" spans="1:12">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -4197,8 +4397,9 @@
       <c r="I211" s="5"/>
       <c r="J211" s="5"/>
       <c r="K211" s="5"/>
-    </row>
-    <row r="212" spans="1:11">
+      <c r="L211" s="5"/>
+    </row>
+    <row r="212" spans="1:12">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -4210,8 +4411,9 @@
       <c r="I212" s="5"/>
       <c r="J212" s="5"/>
       <c r="K212" s="5"/>
-    </row>
-    <row r="213" spans="1:11">
+      <c r="L212" s="5"/>
+    </row>
+    <row r="213" spans="1:12">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -4223,8 +4425,9 @@
       <c r="I213" s="5"/>
       <c r="J213" s="5"/>
       <c r="K213" s="5"/>
-    </row>
-    <row r="214" spans="1:11">
+      <c r="L213" s="5"/>
+    </row>
+    <row r="214" spans="1:12">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -4236,8 +4439,9 @@
       <c r="I214" s="5"/>
       <c r="J214" s="5"/>
       <c r="K214" s="5"/>
-    </row>
-    <row r="215" spans="1:11">
+      <c r="L214" s="5"/>
+    </row>
+    <row r="215" spans="1:12">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -4249,8 +4453,9 @@
       <c r="I215" s="5"/>
       <c r="J215" s="5"/>
       <c r="K215" s="5"/>
-    </row>
-    <row r="216" spans="1:11">
+      <c r="L215" s="5"/>
+    </row>
+    <row r="216" spans="1:12">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -4262,8 +4467,9 @@
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
       <c r="K216" s="5"/>
-    </row>
-    <row r="217" spans="1:11">
+      <c r="L216" s="5"/>
+    </row>
+    <row r="217" spans="1:12">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -4275,8 +4481,9 @@
       <c r="I217" s="5"/>
       <c r="J217" s="5"/>
       <c r="K217" s="5"/>
-    </row>
-    <row r="218" spans="1:11">
+      <c r="L217" s="5"/>
+    </row>
+    <row r="218" spans="1:12">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -4288,8 +4495,9 @@
       <c r="I218" s="5"/>
       <c r="J218" s="5"/>
       <c r="K218" s="5"/>
-    </row>
-    <row r="219" spans="1:11">
+      <c r="L218" s="5"/>
+    </row>
+    <row r="219" spans="1:12">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -4301,8 +4509,9 @@
       <c r="I219" s="5"/>
       <c r="J219" s="5"/>
       <c r="K219" s="5"/>
-    </row>
-    <row r="220" spans="1:11">
+      <c r="L219" s="5"/>
+    </row>
+    <row r="220" spans="1:12">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -4314,8 +4523,9 @@
       <c r="I220" s="5"/>
       <c r="J220" s="5"/>
       <c r="K220" s="5"/>
-    </row>
-    <row r="221" spans="1:11">
+      <c r="L220" s="5"/>
+    </row>
+    <row r="221" spans="1:12">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -4327,8 +4537,9 @@
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
       <c r="K221" s="5"/>
-    </row>
-    <row r="222" spans="1:11">
+      <c r="L221" s="5"/>
+    </row>
+    <row r="222" spans="1:12">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -4340,8 +4551,9 @@
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
       <c r="K222" s="5"/>
-    </row>
-    <row r="223" spans="1:11">
+      <c r="L222" s="5"/>
+    </row>
+    <row r="223" spans="1:12">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -4353,8 +4565,9 @@
       <c r="I223" s="5"/>
       <c r="J223" s="5"/>
       <c r="K223" s="5"/>
-    </row>
-    <row r="224" spans="1:11">
+      <c r="L223" s="5"/>
+    </row>
+    <row r="224" spans="1:12">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -4366,8 +4579,9 @@
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
       <c r="K224" s="5"/>
-    </row>
-    <row r="225" spans="1:11">
+      <c r="L224" s="5"/>
+    </row>
+    <row r="225" spans="1:12">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -4379,8 +4593,9 @@
       <c r="I225" s="5"/>
       <c r="J225" s="5"/>
       <c r="K225" s="5"/>
-    </row>
-    <row r="226" spans="1:11">
+      <c r="L225" s="5"/>
+    </row>
+    <row r="226" spans="1:12">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -4392,8 +4607,9 @@
       <c r="I226" s="5"/>
       <c r="J226" s="5"/>
       <c r="K226" s="5"/>
-    </row>
-    <row r="227" spans="1:11">
+      <c r="L226" s="5"/>
+    </row>
+    <row r="227" spans="1:12">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -4405,8 +4621,9 @@
       <c r="I227" s="5"/>
       <c r="J227" s="5"/>
       <c r="K227" s="5"/>
-    </row>
-    <row r="228" spans="1:11">
+      <c r="L227" s="5"/>
+    </row>
+    <row r="228" spans="1:12">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -4418,8 +4635,9 @@
       <c r="I228" s="5"/>
       <c r="J228" s="5"/>
       <c r="K228" s="5"/>
-    </row>
-    <row r="229" spans="1:11">
+      <c r="L228" s="5"/>
+    </row>
+    <row r="229" spans="1:12">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -4431,8 +4649,9 @@
       <c r="I229" s="5"/>
       <c r="J229" s="5"/>
       <c r="K229" s="5"/>
-    </row>
-    <row r="230" spans="1:11">
+      <c r="L229" s="5"/>
+    </row>
+    <row r="230" spans="1:12">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -4444,8 +4663,9 @@
       <c r="I230" s="5"/>
       <c r="J230" s="5"/>
       <c r="K230" s="5"/>
-    </row>
-    <row r="231" spans="1:11">
+      <c r="L230" s="5"/>
+    </row>
+    <row r="231" spans="1:12">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -4457,8 +4677,9 @@
       <c r="I231" s="5"/>
       <c r="J231" s="5"/>
       <c r="K231" s="5"/>
-    </row>
-    <row r="232" spans="1:11">
+      <c r="L231" s="5"/>
+    </row>
+    <row r="232" spans="1:12">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -4470,8 +4691,9 @@
       <c r="I232" s="5"/>
       <c r="J232" s="5"/>
       <c r="K232" s="5"/>
-    </row>
-    <row r="233" spans="1:11">
+      <c r="L232" s="5"/>
+    </row>
+    <row r="233" spans="1:12">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -4483,8 +4705,9 @@
       <c r="I233" s="5"/>
       <c r="J233" s="5"/>
       <c r="K233" s="5"/>
-    </row>
-    <row r="234" spans="1:11">
+      <c r="L233" s="5"/>
+    </row>
+    <row r="234" spans="1:12">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -4496,8 +4719,9 @@
       <c r="I234" s="5"/>
       <c r="J234" s="5"/>
       <c r="K234" s="5"/>
-    </row>
-    <row r="235" spans="1:11">
+      <c r="L234" s="5"/>
+    </row>
+    <row r="235" spans="1:12">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -4509,8 +4733,9 @@
       <c r="I235" s="5"/>
       <c r="J235" s="5"/>
       <c r="K235" s="5"/>
-    </row>
-    <row r="236" spans="1:11">
+      <c r="L235" s="5"/>
+    </row>
+    <row r="236" spans="1:12">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -4522,8 +4747,9 @@
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
       <c r="K236" s="5"/>
-    </row>
-    <row r="237" spans="1:11">
+      <c r="L236" s="5"/>
+    </row>
+    <row r="237" spans="1:12">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -4535,8 +4761,9 @@
       <c r="I237" s="5"/>
       <c r="J237" s="5"/>
       <c r="K237" s="5"/>
-    </row>
-    <row r="238" spans="1:11">
+      <c r="L237" s="5"/>
+    </row>
+    <row r="238" spans="1:12">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -4548,8 +4775,9 @@
       <c r="I238" s="5"/>
       <c r="J238" s="5"/>
       <c r="K238" s="5"/>
-    </row>
-    <row r="239" spans="1:11">
+      <c r="L238" s="5"/>
+    </row>
+    <row r="239" spans="1:12">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -4561,8 +4789,9 @@
       <c r="I239" s="5"/>
       <c r="J239" s="5"/>
       <c r="K239" s="5"/>
-    </row>
-    <row r="240" spans="1:11">
+      <c r="L239" s="5"/>
+    </row>
+    <row r="240" spans="1:12">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -4574,8 +4803,9 @@
       <c r="I240" s="5"/>
       <c r="J240" s="5"/>
       <c r="K240" s="5"/>
-    </row>
-    <row r="241" spans="1:11">
+      <c r="L240" s="5"/>
+    </row>
+    <row r="241" spans="1:12">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -4587,8 +4817,9 @@
       <c r="I241" s="5"/>
       <c r="J241" s="5"/>
       <c r="K241" s="5"/>
-    </row>
-    <row r="242" spans="1:11">
+      <c r="L241" s="5"/>
+    </row>
+    <row r="242" spans="1:12">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -4600,8 +4831,9 @@
       <c r="I242" s="5"/>
       <c r="J242" s="5"/>
       <c r="K242" s="5"/>
-    </row>
-    <row r="243" spans="1:11">
+      <c r="L242" s="5"/>
+    </row>
+    <row r="243" spans="1:12">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -4613,8 +4845,9 @@
       <c r="I243" s="5"/>
       <c r="J243" s="5"/>
       <c r="K243" s="5"/>
-    </row>
-    <row r="244" spans="1:11">
+      <c r="L243" s="5"/>
+    </row>
+    <row r="244" spans="1:12">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -4626,8 +4859,9 @@
       <c r="I244" s="5"/>
       <c r="J244" s="5"/>
       <c r="K244" s="5"/>
-    </row>
-    <row r="245" spans="1:11">
+      <c r="L244" s="5"/>
+    </row>
+    <row r="245" spans="1:12">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -4639,8 +4873,9 @@
       <c r="I245" s="5"/>
       <c r="J245" s="5"/>
       <c r="K245" s="5"/>
-    </row>
-    <row r="246" spans="1:11">
+      <c r="L245" s="5"/>
+    </row>
+    <row r="246" spans="1:12">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -4652,8 +4887,9 @@
       <c r="I246" s="5"/>
       <c r="J246" s="5"/>
       <c r="K246" s="5"/>
-    </row>
-    <row r="247" spans="1:11">
+      <c r="L246" s="5"/>
+    </row>
+    <row r="247" spans="1:12">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -4665,8 +4901,9 @@
       <c r="I247" s="5"/>
       <c r="J247" s="5"/>
       <c r="K247" s="5"/>
-    </row>
-    <row r="248" spans="1:11">
+      <c r="L247" s="5"/>
+    </row>
+    <row r="248" spans="1:12">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -4678,8 +4915,9 @@
       <c r="I248" s="5"/>
       <c r="J248" s="5"/>
       <c r="K248" s="5"/>
-    </row>
-    <row r="249" spans="1:11">
+      <c r="L248" s="5"/>
+    </row>
+    <row r="249" spans="1:12">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -4691,8 +4929,9 @@
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
       <c r="K249" s="5"/>
-    </row>
-    <row r="250" spans="1:11">
+      <c r="L249" s="5"/>
+    </row>
+    <row r="250" spans="1:12">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -4704,8 +4943,9 @@
       <c r="I250" s="5"/>
       <c r="J250" s="5"/>
       <c r="K250" s="5"/>
-    </row>
-    <row r="251" spans="1:11">
+      <c r="L250" s="5"/>
+    </row>
+    <row r="251" spans="1:12">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -4717,8 +4957,9 @@
       <c r="I251" s="5"/>
       <c r="J251" s="5"/>
       <c r="K251" s="5"/>
-    </row>
-    <row r="252" spans="1:11">
+      <c r="L251" s="5"/>
+    </row>
+    <row r="252" spans="1:12">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -4730,8 +4971,9 @@
       <c r="I252" s="5"/>
       <c r="J252" s="5"/>
       <c r="K252" s="5"/>
-    </row>
-    <row r="253" spans="1:11">
+      <c r="L252" s="5"/>
+    </row>
+    <row r="253" spans="1:12">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -4743,8 +4985,9 @@
       <c r="I253" s="5"/>
       <c r="J253" s="5"/>
       <c r="K253" s="5"/>
-    </row>
-    <row r="254" spans="1:11">
+      <c r="L253" s="5"/>
+    </row>
+    <row r="254" spans="1:12">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -4756,8 +4999,9 @@
       <c r="I254" s="5"/>
       <c r="J254" s="5"/>
       <c r="K254" s="5"/>
-    </row>
-    <row r="255" spans="1:11">
+      <c r="L254" s="5"/>
+    </row>
+    <row r="255" spans="1:12">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -4769,8 +5013,9 @@
       <c r="I255" s="5"/>
       <c r="J255" s="5"/>
       <c r="K255" s="5"/>
-    </row>
-    <row r="256" spans="1:11">
+      <c r="L255" s="5"/>
+    </row>
+    <row r="256" spans="1:12">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -4782,8 +5027,9 @@
       <c r="I256" s="5"/>
       <c r="J256" s="5"/>
       <c r="K256" s="5"/>
-    </row>
-    <row r="257" spans="1:11">
+      <c r="L256" s="5"/>
+    </row>
+    <row r="257" spans="1:12">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -4795,8 +5041,9 @@
       <c r="I257" s="5"/>
       <c r="J257" s="5"/>
       <c r="K257" s="5"/>
-    </row>
-    <row r="258" spans="1:11">
+      <c r="L257" s="5"/>
+    </row>
+    <row r="258" spans="1:12">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -4808,8 +5055,9 @@
       <c r="I258" s="5"/>
       <c r="J258" s="5"/>
       <c r="K258" s="5"/>
-    </row>
-    <row r="259" spans="1:11">
+      <c r="L258" s="5"/>
+    </row>
+    <row r="259" spans="1:12">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -4821,8 +5069,9 @@
       <c r="I259" s="5"/>
       <c r="J259" s="5"/>
       <c r="K259" s="5"/>
-    </row>
-    <row r="260" spans="1:11">
+      <c r="L259" s="5"/>
+    </row>
+    <row r="260" spans="1:12">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -4834,8 +5083,9 @@
       <c r="I260" s="5"/>
       <c r="J260" s="5"/>
       <c r="K260" s="5"/>
-    </row>
-    <row r="261" spans="1:11">
+      <c r="L260" s="5"/>
+    </row>
+    <row r="261" spans="1:12">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -4847,8 +5097,9 @@
       <c r="I261" s="5"/>
       <c r="J261" s="5"/>
       <c r="K261" s="5"/>
-    </row>
-    <row r="262" spans="1:11">
+      <c r="L261" s="5"/>
+    </row>
+    <row r="262" spans="1:12">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -4860,8 +5111,9 @@
       <c r="I262" s="5"/>
       <c r="J262" s="5"/>
       <c r="K262" s="5"/>
-    </row>
-    <row r="263" spans="1:11">
+      <c r="L262" s="5"/>
+    </row>
+    <row r="263" spans="1:12">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -4873,8 +5125,9 @@
       <c r="I263" s="5"/>
       <c r="J263" s="5"/>
       <c r="K263" s="5"/>
-    </row>
-    <row r="264" spans="1:11">
+      <c r="L263" s="5"/>
+    </row>
+    <row r="264" spans="1:12">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -4886,8 +5139,9 @@
       <c r="I264" s="5"/>
       <c r="J264" s="5"/>
       <c r="K264" s="5"/>
-    </row>
-    <row r="265" spans="1:11">
+      <c r="L264" s="5"/>
+    </row>
+    <row r="265" spans="1:12">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -4899,8 +5153,9 @@
       <c r="I265" s="5"/>
       <c r="J265" s="5"/>
       <c r="K265" s="5"/>
-    </row>
-    <row r="266" spans="1:11">
+      <c r="L265" s="5"/>
+    </row>
+    <row r="266" spans="1:12">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -4912,8 +5167,9 @@
       <c r="I266" s="5"/>
       <c r="J266" s="5"/>
       <c r="K266" s="5"/>
-    </row>
-    <row r="267" spans="1:11">
+      <c r="L266" s="5"/>
+    </row>
+    <row r="267" spans="1:12">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -4925,8 +5181,9 @@
       <c r="I267" s="5"/>
       <c r="J267" s="5"/>
       <c r="K267" s="5"/>
-    </row>
-    <row r="268" spans="1:11">
+      <c r="L267" s="5"/>
+    </row>
+    <row r="268" spans="1:12">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -4938,8 +5195,9 @@
       <c r="I268" s="5"/>
       <c r="J268" s="5"/>
       <c r="K268" s="5"/>
-    </row>
-    <row r="269" spans="1:11">
+      <c r="L268" s="5"/>
+    </row>
+    <row r="269" spans="1:12">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -4951,8 +5209,9 @@
       <c r="I269" s="5"/>
       <c r="J269" s="5"/>
       <c r="K269" s="5"/>
-    </row>
-    <row r="270" spans="1:11">
+      <c r="L269" s="5"/>
+    </row>
+    <row r="270" spans="1:12">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -4964,8 +5223,9 @@
       <c r="I270" s="5"/>
       <c r="J270" s="5"/>
       <c r="K270" s="5"/>
-    </row>
-    <row r="271" spans="1:11">
+      <c r="L270" s="5"/>
+    </row>
+    <row r="271" spans="1:12">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -4977,8 +5237,9 @@
       <c r="I271" s="5"/>
       <c r="J271" s="5"/>
       <c r="K271" s="5"/>
-    </row>
-    <row r="272" spans="1:11">
+      <c r="L271" s="5"/>
+    </row>
+    <row r="272" spans="1:12">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -4990,8 +5251,9 @@
       <c r="I272" s="5"/>
       <c r="J272" s="5"/>
       <c r="K272" s="5"/>
-    </row>
-    <row r="273" spans="1:11">
+      <c r="L272" s="5"/>
+    </row>
+    <row r="273" spans="1:12">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -5003,8 +5265,9 @@
       <c r="I273" s="5"/>
       <c r="J273" s="5"/>
       <c r="K273" s="5"/>
-    </row>
-    <row r="274" spans="1:11">
+      <c r="L273" s="5"/>
+    </row>
+    <row r="274" spans="1:12">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -5016,8 +5279,9 @@
       <c r="I274" s="5"/>
       <c r="J274" s="5"/>
       <c r="K274" s="5"/>
-    </row>
-    <row r="275" spans="1:11">
+      <c r="L274" s="5"/>
+    </row>
+    <row r="275" spans="1:12">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -5029,8 +5293,9 @@
       <c r="I275" s="5"/>
       <c r="J275" s="5"/>
       <c r="K275" s="5"/>
-    </row>
-    <row r="276" spans="1:11">
+      <c r="L275" s="5"/>
+    </row>
+    <row r="276" spans="1:12">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -5042,8 +5307,9 @@
       <c r="I276" s="5"/>
       <c r="J276" s="5"/>
       <c r="K276" s="5"/>
-    </row>
-    <row r="277" spans="1:11">
+      <c r="L276" s="5"/>
+    </row>
+    <row r="277" spans="1:12">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -5055,8 +5321,9 @@
       <c r="I277" s="5"/>
       <c r="J277" s="5"/>
       <c r="K277" s="5"/>
-    </row>
-    <row r="278" spans="1:11">
+      <c r="L277" s="5"/>
+    </row>
+    <row r="278" spans="1:12">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -5068,8 +5335,9 @@
       <c r="I278" s="5"/>
       <c r="J278" s="5"/>
       <c r="K278" s="5"/>
-    </row>
-    <row r="279" spans="1:11">
+      <c r="L278" s="5"/>
+    </row>
+    <row r="279" spans="1:12">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -5081,8 +5349,9 @@
       <c r="I279" s="5"/>
       <c r="J279" s="5"/>
       <c r="K279" s="5"/>
-    </row>
-    <row r="280" spans="1:11">
+      <c r="L279" s="5"/>
+    </row>
+    <row r="280" spans="1:12">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -5094,8 +5363,9 @@
       <c r="I280" s="5"/>
       <c r="J280" s="5"/>
       <c r="K280" s="5"/>
-    </row>
-    <row r="281" spans="1:11">
+      <c r="L280" s="5"/>
+    </row>
+    <row r="281" spans="1:12">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -5107,8 +5377,9 @@
       <c r="I281" s="5"/>
       <c r="J281" s="5"/>
       <c r="K281" s="5"/>
-    </row>
-    <row r="282" spans="1:11">
+      <c r="L281" s="5"/>
+    </row>
+    <row r="282" spans="1:12">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -5120,8 +5391,9 @@
       <c r="I282" s="5"/>
       <c r="J282" s="5"/>
       <c r="K282" s="5"/>
-    </row>
-    <row r="283" spans="1:11">
+      <c r="L282" s="5"/>
+    </row>
+    <row r="283" spans="1:12">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -5133,8 +5405,9 @@
       <c r="I283" s="5"/>
       <c r="J283" s="5"/>
       <c r="K283" s="5"/>
-    </row>
-    <row r="284" spans="1:11">
+      <c r="L283" s="5"/>
+    </row>
+    <row r="284" spans="1:12">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -5146,8 +5419,9 @@
       <c r="I284" s="5"/>
       <c r="J284" s="5"/>
       <c r="K284" s="5"/>
-    </row>
-    <row r="285" spans="1:11">
+      <c r="L284" s="5"/>
+    </row>
+    <row r="285" spans="1:12">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -5159,8 +5433,9 @@
       <c r="I285" s="5"/>
       <c r="J285" s="5"/>
       <c r="K285" s="5"/>
-    </row>
-    <row r="286" spans="1:11">
+      <c r="L285" s="5"/>
+    </row>
+    <row r="286" spans="1:12">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -5172,8 +5447,9 @@
       <c r="I286" s="5"/>
       <c r="J286" s="5"/>
       <c r="K286" s="5"/>
-    </row>
-    <row r="287" spans="1:11">
+      <c r="L286" s="5"/>
+    </row>
+    <row r="287" spans="1:12">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -5185,8 +5461,9 @@
       <c r="I287" s="5"/>
       <c r="J287" s="5"/>
       <c r="K287" s="5"/>
-    </row>
-    <row r="288" spans="1:11">
+      <c r="L287" s="5"/>
+    </row>
+    <row r="288" spans="1:12">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -5198,8 +5475,9 @@
       <c r="I288" s="5"/>
       <c r="J288" s="5"/>
       <c r="K288" s="5"/>
-    </row>
-    <row r="289" spans="1:11">
+      <c r="L288" s="5"/>
+    </row>
+    <row r="289" spans="1:12">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -5211,8 +5489,9 @@
       <c r="I289" s="5"/>
       <c r="J289" s="5"/>
       <c r="K289" s="5"/>
-    </row>
-    <row r="290" spans="1:11">
+      <c r="L289" s="5"/>
+    </row>
+    <row r="290" spans="1:12">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -5224,8 +5503,9 @@
       <c r="I290" s="5"/>
       <c r="J290" s="5"/>
       <c r="K290" s="5"/>
-    </row>
-    <row r="291" spans="1:11">
+      <c r="L290" s="5"/>
+    </row>
+    <row r="291" spans="1:12">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -5237,8 +5517,9 @@
       <c r="I291" s="5"/>
       <c r="J291" s="5"/>
       <c r="K291" s="5"/>
-    </row>
-    <row r="292" spans="1:11">
+      <c r="L291" s="5"/>
+    </row>
+    <row r="292" spans="1:12">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -5250,8 +5531,9 @@
       <c r="I292" s="5"/>
       <c r="J292" s="5"/>
       <c r="K292" s="5"/>
-    </row>
-    <row r="293" spans="1:11">
+      <c r="L292" s="5"/>
+    </row>
+    <row r="293" spans="1:12">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -5263,8 +5545,9 @@
       <c r="I293" s="5"/>
       <c r="J293" s="5"/>
       <c r="K293" s="5"/>
-    </row>
-    <row r="294" spans="1:11">
+      <c r="L293" s="5"/>
+    </row>
+    <row r="294" spans="1:12">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -5276,8 +5559,9 @@
       <c r="I294" s="5"/>
       <c r="J294" s="5"/>
       <c r="K294" s="5"/>
-    </row>
-    <row r="295" spans="1:11">
+      <c r="L294" s="5"/>
+    </row>
+    <row r="295" spans="1:12">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -5289,8 +5573,9 @@
       <c r="I295" s="5"/>
       <c r="J295" s="5"/>
       <c r="K295" s="5"/>
-    </row>
-    <row r="296" spans="1:11">
+      <c r="L295" s="5"/>
+    </row>
+    <row r="296" spans="1:12">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -5302,8 +5587,9 @@
       <c r="I296" s="5"/>
       <c r="J296" s="5"/>
       <c r="K296" s="5"/>
-    </row>
-    <row r="297" spans="1:11">
+      <c r="L296" s="5"/>
+    </row>
+    <row r="297" spans="1:12">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -5315,8 +5601,9 @@
       <c r="I297" s="5"/>
       <c r="J297" s="5"/>
       <c r="K297" s="5"/>
-    </row>
-    <row r="298" spans="1:11">
+      <c r="L297" s="5"/>
+    </row>
+    <row r="298" spans="1:12">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -5328,8 +5615,9 @@
       <c r="I298" s="5"/>
       <c r="J298" s="5"/>
       <c r="K298" s="5"/>
-    </row>
-    <row r="299" spans="1:11">
+      <c r="L298" s="5"/>
+    </row>
+    <row r="299" spans="1:12">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -5341,8 +5629,9 @@
       <c r="I299" s="5"/>
       <c r="J299" s="5"/>
       <c r="K299" s="5"/>
-    </row>
-    <row r="300" spans="1:11">
+      <c r="L299" s="5"/>
+    </row>
+    <row r="300" spans="1:12">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -5354,8 +5643,9 @@
       <c r="I300" s="5"/>
       <c r="J300" s="5"/>
       <c r="K300" s="5"/>
-    </row>
-    <row r="301" spans="1:11">
+      <c r="L300" s="5"/>
+    </row>
+    <row r="301" spans="1:12">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -5367,8 +5657,9 @@
       <c r="I301" s="5"/>
       <c r="J301" s="5"/>
       <c r="K301" s="5"/>
-    </row>
-    <row r="302" spans="1:11">
+      <c r="L301" s="5"/>
+    </row>
+    <row r="302" spans="1:12">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -5380,8 +5671,9 @@
       <c r="I302" s="5"/>
       <c r="J302" s="5"/>
       <c r="K302" s="5"/>
-    </row>
-    <row r="303" spans="1:11">
+      <c r="L302" s="5"/>
+    </row>
+    <row r="303" spans="1:12">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -5393,8 +5685,9 @@
       <c r="I303" s="5"/>
       <c r="J303" s="5"/>
       <c r="K303" s="5"/>
-    </row>
-    <row r="304" spans="1:11">
+      <c r="L303" s="5"/>
+    </row>
+    <row r="304" spans="1:12">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -5406,8 +5699,9 @@
       <c r="I304" s="5"/>
       <c r="J304" s="5"/>
       <c r="K304" s="5"/>
-    </row>
-    <row r="305" spans="1:11">
+      <c r="L304" s="5"/>
+    </row>
+    <row r="305" spans="1:12">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -5419,8 +5713,9 @@
       <c r="I305" s="5"/>
       <c r="J305" s="5"/>
       <c r="K305" s="5"/>
-    </row>
-    <row r="306" spans="1:11">
+      <c r="L305" s="5"/>
+    </row>
+    <row r="306" spans="1:12">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -5432,8 +5727,9 @@
       <c r="I306" s="5"/>
       <c r="J306" s="5"/>
       <c r="K306" s="5"/>
-    </row>
-    <row r="307" spans="1:11">
+      <c r="L306" s="5"/>
+    </row>
+    <row r="307" spans="1:12">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -5445,8 +5741,9 @@
       <c r="I307" s="5"/>
       <c r="J307" s="5"/>
       <c r="K307" s="5"/>
-    </row>
-    <row r="308" spans="1:11">
+      <c r="L307" s="5"/>
+    </row>
+    <row r="308" spans="1:12">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -5458,8 +5755,9 @@
       <c r="I308" s="5"/>
       <c r="J308" s="5"/>
       <c r="K308" s="5"/>
-    </row>
-    <row r="309" spans="1:11">
+      <c r="L308" s="5"/>
+    </row>
+    <row r="309" spans="1:12">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -5471,8 +5769,9 @@
       <c r="I309" s="5"/>
       <c r="J309" s="5"/>
       <c r="K309" s="5"/>
-    </row>
-    <row r="310" spans="1:11">
+      <c r="L309" s="5"/>
+    </row>
+    <row r="310" spans="1:12">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -5484,8 +5783,9 @@
       <c r="I310" s="5"/>
       <c r="J310" s="5"/>
       <c r="K310" s="5"/>
-    </row>
-    <row r="311" spans="1:11">
+      <c r="L310" s="5"/>
+    </row>
+    <row r="311" spans="1:12">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -5497,8 +5797,9 @@
       <c r="I311" s="5"/>
       <c r="J311" s="5"/>
       <c r="K311" s="5"/>
-    </row>
-    <row r="312" spans="1:11">
+      <c r="L311" s="5"/>
+    </row>
+    <row r="312" spans="1:12">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -5510,8 +5811,9 @@
       <c r="I312" s="5"/>
       <c r="J312" s="5"/>
       <c r="K312" s="5"/>
-    </row>
-    <row r="313" spans="1:11">
+      <c r="L312" s="5"/>
+    </row>
+    <row r="313" spans="1:12">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -5523,8 +5825,9 @@
       <c r="I313" s="5"/>
       <c r="J313" s="5"/>
       <c r="K313" s="5"/>
-    </row>
-    <row r="314" spans="1:11">
+      <c r="L313" s="5"/>
+    </row>
+    <row r="314" spans="1:12">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -5536,8 +5839,9 @@
       <c r="I314" s="5"/>
       <c r="J314" s="5"/>
       <c r="K314" s="5"/>
-    </row>
-    <row r="315" spans="1:11">
+      <c r="L314" s="5"/>
+    </row>
+    <row r="315" spans="1:12">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -5549,8 +5853,9 @@
       <c r="I315" s="5"/>
       <c r="J315" s="5"/>
       <c r="K315" s="5"/>
-    </row>
-    <row r="316" spans="1:11">
+      <c r="L315" s="5"/>
+    </row>
+    <row r="316" spans="1:12">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -5562,8 +5867,9 @@
       <c r="I316" s="5"/>
       <c r="J316" s="5"/>
       <c r="K316" s="5"/>
-    </row>
-    <row r="317" spans="1:11">
+      <c r="L316" s="5"/>
+    </row>
+    <row r="317" spans="1:12">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -5575,8 +5881,9 @@
       <c r="I317" s="5"/>
       <c r="J317" s="5"/>
       <c r="K317" s="5"/>
-    </row>
-    <row r="318" spans="1:11">
+      <c r="L317" s="5"/>
+    </row>
+    <row r="318" spans="1:12">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -5588,8 +5895,9 @@
       <c r="I318" s="5"/>
       <c r="J318" s="5"/>
       <c r="K318" s="5"/>
-    </row>
-    <row r="319" spans="1:11">
+      <c r="L318" s="5"/>
+    </row>
+    <row r="319" spans="1:12">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -5601,8 +5909,9 @@
       <c r="I319" s="5"/>
       <c r="J319" s="5"/>
       <c r="K319" s="5"/>
-    </row>
-    <row r="320" spans="1:11">
+      <c r="L319" s="5"/>
+    </row>
+    <row r="320" spans="1:12">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -5614,8 +5923,9 @@
       <c r="I320" s="5"/>
       <c r="J320" s="5"/>
       <c r="K320" s="5"/>
-    </row>
-    <row r="321" spans="1:11">
+      <c r="L320" s="5"/>
+    </row>
+    <row r="321" spans="1:12">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -5627,8 +5937,9 @@
       <c r="I321" s="5"/>
       <c r="J321" s="5"/>
       <c r="K321" s="5"/>
-    </row>
-    <row r="322" spans="1:11">
+      <c r="L321" s="5"/>
+    </row>
+    <row r="322" spans="1:12">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -5640,8 +5951,9 @@
       <c r="I322" s="5"/>
       <c r="J322" s="5"/>
       <c r="K322" s="5"/>
-    </row>
-    <row r="323" spans="1:11">
+      <c r="L322" s="5"/>
+    </row>
+    <row r="323" spans="1:12">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -5653,8 +5965,9 @@
       <c r="I323" s="5"/>
       <c r="J323" s="5"/>
       <c r="K323" s="5"/>
-    </row>
-    <row r="324" spans="1:11">
+      <c r="L323" s="5"/>
+    </row>
+    <row r="324" spans="1:12">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -5666,8 +5979,9 @@
       <c r="I324" s="5"/>
       <c r="J324" s="5"/>
       <c r="K324" s="5"/>
-    </row>
-    <row r="325" spans="1:11">
+      <c r="L324" s="5"/>
+    </row>
+    <row r="325" spans="1:12">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -5679,8 +5993,9 @@
       <c r="I325" s="5"/>
       <c r="J325" s="5"/>
       <c r="K325" s="5"/>
-    </row>
-    <row r="326" spans="1:11">
+      <c r="L325" s="5"/>
+    </row>
+    <row r="326" spans="1:12">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -5692,8 +6007,9 @@
       <c r="I326" s="5"/>
       <c r="J326" s="5"/>
       <c r="K326" s="5"/>
-    </row>
-    <row r="327" spans="1:11">
+      <c r="L326" s="5"/>
+    </row>
+    <row r="327" spans="1:12">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -5705,8 +6021,9 @@
       <c r="I327" s="5"/>
       <c r="J327" s="5"/>
       <c r="K327" s="5"/>
-    </row>
-    <row r="328" spans="1:11">
+      <c r="L327" s="5"/>
+    </row>
+    <row r="328" spans="1:12">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -5718,8 +6035,9 @@
       <c r="I328" s="5"/>
       <c r="J328" s="5"/>
       <c r="K328" s="5"/>
-    </row>
-    <row r="329" spans="1:11">
+      <c r="L328" s="5"/>
+    </row>
+    <row r="329" spans="1:12">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -5731,8 +6049,9 @@
       <c r="I329" s="5"/>
       <c r="J329" s="5"/>
       <c r="K329" s="5"/>
-    </row>
-    <row r="330" spans="1:11">
+      <c r="L329" s="5"/>
+    </row>
+    <row r="330" spans="1:12">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -5744,8 +6063,9 @@
       <c r="I330" s="5"/>
       <c r="J330" s="5"/>
       <c r="K330" s="5"/>
-    </row>
-    <row r="331" spans="1:11">
+      <c r="L330" s="5"/>
+    </row>
+    <row r="331" spans="1:12">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -5757,8 +6077,9 @@
       <c r="I331" s="5"/>
       <c r="J331" s="5"/>
       <c r="K331" s="5"/>
-    </row>
-    <row r="332" spans="1:11">
+      <c r="L331" s="5"/>
+    </row>
+    <row r="332" spans="1:12">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -5770,8 +6091,9 @@
       <c r="I332" s="5"/>
       <c r="J332" s="5"/>
       <c r="K332" s="5"/>
-    </row>
-    <row r="333" spans="1:11">
+      <c r="L332" s="5"/>
+    </row>
+    <row r="333" spans="1:12">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -5783,8 +6105,9 @@
       <c r="I333" s="5"/>
       <c r="J333" s="5"/>
       <c r="K333" s="5"/>
-    </row>
-    <row r="334" spans="1:11">
+      <c r="L333" s="5"/>
+    </row>
+    <row r="334" spans="1:12">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -5796,8 +6119,9 @@
       <c r="I334" s="5"/>
       <c r="J334" s="5"/>
       <c r="K334" s="5"/>
-    </row>
-    <row r="335" spans="1:11">
+      <c r="L334" s="5"/>
+    </row>
+    <row r="335" spans="1:12">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -5809,8 +6133,9 @@
       <c r="I335" s="5"/>
       <c r="J335" s="5"/>
       <c r="K335" s="5"/>
-    </row>
-    <row r="336" spans="1:11">
+      <c r="L335" s="5"/>
+    </row>
+    <row r="336" spans="1:12">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -5822,8 +6147,9 @@
       <c r="I336" s="5"/>
       <c r="J336" s="5"/>
       <c r="K336" s="5"/>
-    </row>
-    <row r="337" spans="1:11">
+      <c r="L336" s="5"/>
+    </row>
+    <row r="337" spans="1:12">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -5835,8 +6161,9 @@
       <c r="I337" s="5"/>
       <c r="J337" s="5"/>
       <c r="K337" s="5"/>
-    </row>
-    <row r="338" spans="1:11">
+      <c r="L337" s="5"/>
+    </row>
+    <row r="338" spans="1:12">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -5848,8 +6175,9 @@
       <c r="I338" s="5"/>
       <c r="J338" s="5"/>
       <c r="K338" s="5"/>
-    </row>
-    <row r="339" spans="1:11">
+      <c r="L338" s="5"/>
+    </row>
+    <row r="339" spans="1:12">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -5861,8 +6189,9 @@
       <c r="I339" s="5"/>
       <c r="J339" s="5"/>
       <c r="K339" s="5"/>
-    </row>
-    <row r="340" spans="1:11">
+      <c r="L339" s="5"/>
+    </row>
+    <row r="340" spans="1:12">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -5874,8 +6203,9 @@
       <c r="I340" s="5"/>
       <c r="J340" s="5"/>
       <c r="K340" s="5"/>
-    </row>
-    <row r="341" spans="1:11">
+      <c r="L340" s="5"/>
+    </row>
+    <row r="341" spans="1:12">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -5887,8 +6217,9 @@
       <c r="I341" s="5"/>
       <c r="J341" s="5"/>
       <c r="K341" s="5"/>
-    </row>
-    <row r="342" spans="1:11">
+      <c r="L341" s="5"/>
+    </row>
+    <row r="342" spans="1:12">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -5900,8 +6231,9 @@
       <c r="I342" s="5"/>
       <c r="J342" s="5"/>
       <c r="K342" s="5"/>
-    </row>
-    <row r="343" spans="1:11">
+      <c r="L342" s="5"/>
+    </row>
+    <row r="343" spans="1:12">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -5913,8 +6245,9 @@
       <c r="I343" s="5"/>
       <c r="J343" s="5"/>
       <c r="K343" s="5"/>
-    </row>
-    <row r="344" spans="1:11">
+      <c r="L343" s="5"/>
+    </row>
+    <row r="344" spans="1:12">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -5926,8 +6259,9 @@
       <c r="I344" s="5"/>
       <c r="J344" s="5"/>
       <c r="K344" s="5"/>
-    </row>
-    <row r="345" spans="1:11">
+      <c r="L344" s="5"/>
+    </row>
+    <row r="345" spans="1:12">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -5939,8 +6273,9 @@
       <c r="I345" s="5"/>
       <c r="J345" s="5"/>
       <c r="K345" s="5"/>
-    </row>
-    <row r="346" spans="1:11">
+      <c r="L345" s="5"/>
+    </row>
+    <row r="346" spans="1:12">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -5952,8 +6287,9 @@
       <c r="I346" s="5"/>
       <c r="J346" s="5"/>
       <c r="K346" s="5"/>
-    </row>
-    <row r="347" spans="1:11">
+      <c r="L346" s="5"/>
+    </row>
+    <row r="347" spans="1:12">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -5965,8 +6301,9 @@
       <c r="I347" s="5"/>
       <c r="J347" s="5"/>
       <c r="K347" s="5"/>
-    </row>
-    <row r="348" spans="1:11">
+      <c r="L347" s="5"/>
+    </row>
+    <row r="348" spans="1:12">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -5978,8 +6315,9 @@
       <c r="I348" s="5"/>
       <c r="J348" s="5"/>
       <c r="K348" s="5"/>
-    </row>
-    <row r="349" spans="1:11">
+      <c r="L348" s="5"/>
+    </row>
+    <row r="349" spans="1:12">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -5991,8 +6329,9 @@
       <c r="I349" s="5"/>
       <c r="J349" s="5"/>
       <c r="K349" s="5"/>
-    </row>
-    <row r="350" spans="1:11">
+      <c r="L349" s="5"/>
+    </row>
+    <row r="350" spans="1:12">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -6004,8 +6343,9 @@
       <c r="I350" s="5"/>
       <c r="J350" s="5"/>
       <c r="K350" s="5"/>
-    </row>
-    <row r="351" spans="1:11">
+      <c r="L350" s="5"/>
+    </row>
+    <row r="351" spans="1:12">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -6017,8 +6357,9 @@
       <c r="I351" s="5"/>
       <c r="J351" s="5"/>
       <c r="K351" s="5"/>
-    </row>
-    <row r="352" spans="1:11">
+      <c r="L351" s="5"/>
+    </row>
+    <row r="352" spans="1:12">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -6030,8 +6371,9 @@
       <c r="I352" s="5"/>
       <c r="J352" s="5"/>
       <c r="K352" s="5"/>
-    </row>
-    <row r="353" spans="1:11">
+      <c r="L352" s="5"/>
+    </row>
+    <row r="353" spans="1:12">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -6043,8 +6385,9 @@
       <c r="I353" s="5"/>
       <c r="J353" s="5"/>
       <c r="K353" s="5"/>
-    </row>
-    <row r="354" spans="1:11">
+      <c r="L353" s="5"/>
+    </row>
+    <row r="354" spans="1:12">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -6056,8 +6399,9 @@
       <c r="I354" s="5"/>
       <c r="J354" s="5"/>
       <c r="K354" s="5"/>
-    </row>
-    <row r="355" spans="1:11">
+      <c r="L354" s="5"/>
+    </row>
+    <row r="355" spans="1:12">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -6069,8 +6413,9 @@
       <c r="I355" s="5"/>
       <c r="J355" s="5"/>
       <c r="K355" s="5"/>
-    </row>
-    <row r="356" spans="1:11">
+      <c r="L355" s="5"/>
+    </row>
+    <row r="356" spans="1:12">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -6082,8 +6427,9 @@
       <c r="I356" s="5"/>
       <c r="J356" s="5"/>
       <c r="K356" s="5"/>
-    </row>
-    <row r="357" spans="1:11">
+      <c r="L356" s="5"/>
+    </row>
+    <row r="357" spans="1:12">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -6095,8 +6441,9 @@
       <c r="I357" s="5"/>
       <c r="J357" s="5"/>
       <c r="K357" s="5"/>
-    </row>
-    <row r="358" spans="1:11">
+      <c r="L357" s="5"/>
+    </row>
+    <row r="358" spans="1:12">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -6108,8 +6455,9 @@
       <c r="I358" s="5"/>
       <c r="J358" s="5"/>
       <c r="K358" s="5"/>
-    </row>
-    <row r="359" spans="1:11">
+      <c r="L358" s="5"/>
+    </row>
+    <row r="359" spans="1:12">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -6121,8 +6469,9 @@
       <c r="I359" s="5"/>
       <c r="J359" s="5"/>
       <c r="K359" s="5"/>
-    </row>
-    <row r="360" spans="1:11">
+      <c r="L359" s="5"/>
+    </row>
+    <row r="360" spans="1:12">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -6134,8 +6483,9 @@
       <c r="I360" s="5"/>
       <c r="J360" s="5"/>
       <c r="K360" s="5"/>
-    </row>
-    <row r="361" spans="1:11">
+      <c r="L360" s="5"/>
+    </row>
+    <row r="361" spans="1:12">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -6147,8 +6497,9 @@
       <c r="I361" s="5"/>
       <c r="J361" s="5"/>
       <c r="K361" s="5"/>
-    </row>
-    <row r="362" spans="1:11">
+      <c r="L361" s="5"/>
+    </row>
+    <row r="362" spans="1:12">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -6160,8 +6511,9 @@
       <c r="I362" s="5"/>
       <c r="J362" s="5"/>
       <c r="K362" s="5"/>
-    </row>
-    <row r="363" spans="1:11">
+      <c r="L362" s="5"/>
+    </row>
+    <row r="363" spans="1:12">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -6173,8 +6525,9 @@
       <c r="I363" s="5"/>
       <c r="J363" s="5"/>
       <c r="K363" s="5"/>
-    </row>
-    <row r="364" spans="1:11">
+      <c r="L363" s="5"/>
+    </row>
+    <row r="364" spans="1:12">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -6186,8 +6539,9 @@
       <c r="I364" s="5"/>
       <c r="J364" s="5"/>
       <c r="K364" s="5"/>
-    </row>
-    <row r="365" spans="1:11">
+      <c r="L364" s="5"/>
+    </row>
+    <row r="365" spans="1:12">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -6199,8 +6553,9 @@
       <c r="I365" s="5"/>
       <c r="J365" s="5"/>
       <c r="K365" s="5"/>
-    </row>
-    <row r="366" spans="1:11">
+      <c r="L365" s="5"/>
+    </row>
+    <row r="366" spans="1:12">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -6212,8 +6567,9 @@
       <c r="I366" s="5"/>
       <c r="J366" s="5"/>
       <c r="K366" s="5"/>
-    </row>
-    <row r="367" spans="1:11">
+      <c r="L366" s="5"/>
+    </row>
+    <row r="367" spans="1:12">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -6225,8 +6581,9 @@
       <c r="I367" s="5"/>
       <c r="J367" s="5"/>
       <c r="K367" s="5"/>
-    </row>
-    <row r="368" spans="1:11">
+      <c r="L367" s="5"/>
+    </row>
+    <row r="368" spans="1:12">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -6238,8 +6595,9 @@
       <c r="I368" s="5"/>
       <c r="J368" s="5"/>
       <c r="K368" s="5"/>
-    </row>
-    <row r="369" spans="1:11">
+      <c r="L368" s="5"/>
+    </row>
+    <row r="369" spans="1:12">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -6251,8 +6609,9 @@
       <c r="I369" s="5"/>
       <c r="J369" s="5"/>
       <c r="K369" s="5"/>
-    </row>
-    <row r="370" spans="1:11">
+      <c r="L369" s="5"/>
+    </row>
+    <row r="370" spans="1:12">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -6264,8 +6623,9 @@
       <c r="I370" s="5"/>
       <c r="J370" s="5"/>
       <c r="K370" s="5"/>
-    </row>
-    <row r="371" spans="1:11">
+      <c r="L370" s="5"/>
+    </row>
+    <row r="371" spans="1:12">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -6277,8 +6637,9 @@
       <c r="I371" s="5"/>
       <c r="J371" s="5"/>
       <c r="K371" s="5"/>
-    </row>
-    <row r="372" spans="1:11">
+      <c r="L371" s="5"/>
+    </row>
+    <row r="372" spans="1:12">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -6290,8 +6651,9 @@
       <c r="I372" s="5"/>
       <c r="J372" s="5"/>
       <c r="K372" s="5"/>
-    </row>
-    <row r="373" spans="1:11">
+      <c r="L372" s="5"/>
+    </row>
+    <row r="373" spans="1:12">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -6303,8 +6665,9 @@
       <c r="I373" s="5"/>
       <c r="J373" s="5"/>
       <c r="K373" s="5"/>
-    </row>
-    <row r="374" spans="1:11">
+      <c r="L373" s="5"/>
+    </row>
+    <row r="374" spans="1:12">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -6316,8 +6679,9 @@
       <c r="I374" s="5"/>
       <c r="J374" s="5"/>
       <c r="K374" s="5"/>
-    </row>
-    <row r="375" spans="1:11">
+      <c r="L374" s="5"/>
+    </row>
+    <row r="375" spans="1:12">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -6329,8 +6693,9 @@
       <c r="I375" s="5"/>
       <c r="J375" s="5"/>
       <c r="K375" s="5"/>
-    </row>
-    <row r="376" spans="1:11">
+      <c r="L375" s="5"/>
+    </row>
+    <row r="376" spans="1:12">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -6342,8 +6707,9 @@
       <c r="I376" s="5"/>
       <c r="J376" s="5"/>
       <c r="K376" s="5"/>
-    </row>
-    <row r="377" spans="1:11">
+      <c r="L376" s="5"/>
+    </row>
+    <row r="377" spans="1:12">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -6355,8 +6721,9 @@
       <c r="I377" s="5"/>
       <c r="J377" s="5"/>
       <c r="K377" s="5"/>
-    </row>
-    <row r="378" spans="1:11">
+      <c r="L377" s="5"/>
+    </row>
+    <row r="378" spans="1:12">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -6368,8 +6735,9 @@
       <c r="I378" s="5"/>
       <c r="J378" s="5"/>
       <c r="K378" s="5"/>
-    </row>
-    <row r="379" spans="1:11">
+      <c r="L378" s="5"/>
+    </row>
+    <row r="379" spans="1:12">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -6381,8 +6749,9 @@
       <c r="I379" s="5"/>
       <c r="J379" s="5"/>
       <c r="K379" s="5"/>
-    </row>
-    <row r="380" spans="1:11">
+      <c r="L379" s="5"/>
+    </row>
+    <row r="380" spans="1:12">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -6394,8 +6763,9 @@
       <c r="I380" s="5"/>
       <c r="J380" s="5"/>
       <c r="K380" s="5"/>
-    </row>
-    <row r="381" spans="1:11">
+      <c r="L380" s="5"/>
+    </row>
+    <row r="381" spans="1:12">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -6407,8 +6777,9 @@
       <c r="I381" s="5"/>
       <c r="J381" s="5"/>
       <c r="K381" s="5"/>
-    </row>
-    <row r="382" spans="1:11">
+      <c r="L381" s="5"/>
+    </row>
+    <row r="382" spans="1:12">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -6420,8 +6791,9 @@
       <c r="I382" s="5"/>
       <c r="J382" s="5"/>
       <c r="K382" s="5"/>
-    </row>
-    <row r="383" spans="1:11">
+      <c r="L382" s="5"/>
+    </row>
+    <row r="383" spans="1:12">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -6433,8 +6805,9 @@
       <c r="I383" s="5"/>
       <c r="J383" s="5"/>
       <c r="K383" s="5"/>
-    </row>
-    <row r="384" spans="1:11">
+      <c r="L383" s="5"/>
+    </row>
+    <row r="384" spans="1:12">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -6446,8 +6819,9 @@
       <c r="I384" s="5"/>
       <c r="J384" s="5"/>
       <c r="K384" s="5"/>
-    </row>
-    <row r="385" spans="1:11">
+      <c r="L384" s="5"/>
+    </row>
+    <row r="385" spans="1:12">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -6459,8 +6833,9 @@
       <c r="I385" s="5"/>
       <c r="J385" s="5"/>
       <c r="K385" s="5"/>
-    </row>
-    <row r="386" spans="1:11">
+      <c r="L385" s="5"/>
+    </row>
+    <row r="386" spans="1:12">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -6472,8 +6847,9 @@
       <c r="I386" s="5"/>
       <c r="J386" s="5"/>
       <c r="K386" s="5"/>
-    </row>
-    <row r="387" spans="1:11">
+      <c r="L386" s="5"/>
+    </row>
+    <row r="387" spans="1:12">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -6485,8 +6861,9 @@
       <c r="I387" s="5"/>
       <c r="J387" s="5"/>
       <c r="K387" s="5"/>
-    </row>
-    <row r="388" spans="1:11">
+      <c r="L387" s="5"/>
+    </row>
+    <row r="388" spans="1:12">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -6498,8 +6875,9 @@
       <c r="I388" s="5"/>
       <c r="J388" s="5"/>
       <c r="K388" s="5"/>
-    </row>
-    <row r="389" spans="1:11">
+      <c r="L388" s="5"/>
+    </row>
+    <row r="389" spans="1:12">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -6511,8 +6889,9 @@
       <c r="I389" s="5"/>
       <c r="J389" s="5"/>
       <c r="K389" s="5"/>
-    </row>
-    <row r="390" spans="1:11">
+      <c r="L389" s="5"/>
+    </row>
+    <row r="390" spans="1:12">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -6524,8 +6903,9 @@
       <c r="I390" s="5"/>
       <c r="J390" s="5"/>
       <c r="K390" s="5"/>
-    </row>
-    <row r="391" spans="1:11">
+      <c r="L390" s="5"/>
+    </row>
+    <row r="391" spans="1:12">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -6537,8 +6917,9 @@
       <c r="I391" s="5"/>
       <c r="J391" s="5"/>
       <c r="K391" s="5"/>
-    </row>
-    <row r="392" spans="1:11">
+      <c r="L391" s="5"/>
+    </row>
+    <row r="392" spans="1:12">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -6550,8 +6931,9 @@
       <c r="I392" s="5"/>
       <c r="J392" s="5"/>
       <c r="K392" s="5"/>
-    </row>
-    <row r="393" spans="1:11">
+      <c r="L392" s="5"/>
+    </row>
+    <row r="393" spans="1:12">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -6563,8 +6945,9 @@
       <c r="I393" s="5"/>
       <c r="J393" s="5"/>
       <c r="K393" s="5"/>
-    </row>
-    <row r="394" spans="1:11">
+      <c r="L393" s="5"/>
+    </row>
+    <row r="394" spans="1:12">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -6576,8 +6959,9 @@
       <c r="I394" s="5"/>
       <c r="J394" s="5"/>
       <c r="K394" s="5"/>
-    </row>
-    <row r="395" spans="1:11">
+      <c r="L394" s="5"/>
+    </row>
+    <row r="395" spans="1:12">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -6589,8 +6973,9 @@
       <c r="I395" s="5"/>
       <c r="J395" s="5"/>
       <c r="K395" s="5"/>
-    </row>
-    <row r="396" spans="1:11">
+      <c r="L395" s="5"/>
+    </row>
+    <row r="396" spans="1:12">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -6602,8 +6987,9 @@
       <c r="I396" s="5"/>
       <c r="J396" s="5"/>
       <c r="K396" s="5"/>
-    </row>
-    <row r="397" spans="1:11">
+      <c r="L396" s="5"/>
+    </row>
+    <row r="397" spans="1:12">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -6615,8 +7001,9 @@
       <c r="I397" s="5"/>
       <c r="J397" s="5"/>
       <c r="K397" s="5"/>
-    </row>
-    <row r="398" spans="1:11">
+      <c r="L397" s="5"/>
+    </row>
+    <row r="398" spans="1:12">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -6628,8 +7015,9 @@
       <c r="I398" s="5"/>
       <c r="J398" s="5"/>
       <c r="K398" s="5"/>
-    </row>
-    <row r="399" spans="1:11">
+      <c r="L398" s="5"/>
+    </row>
+    <row r="399" spans="1:12">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -6641,8 +7029,9 @@
       <c r="I399" s="5"/>
       <c r="J399" s="5"/>
       <c r="K399" s="5"/>
-    </row>
-    <row r="400" spans="1:11">
+      <c r="L399" s="5"/>
+    </row>
+    <row r="400" spans="1:12">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -6654,8 +7043,9 @@
       <c r="I400" s="5"/>
       <c r="J400" s="5"/>
       <c r="K400" s="5"/>
-    </row>
-    <row r="401" spans="1:11">
+      <c r="L400" s="5"/>
+    </row>
+    <row r="401" spans="1:12">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -6667,8 +7057,9 @@
       <c r="I401" s="5"/>
       <c r="J401" s="5"/>
       <c r="K401" s="5"/>
-    </row>
-    <row r="402" spans="1:11">
+      <c r="L401" s="5"/>
+    </row>
+    <row r="402" spans="1:12">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -6680,8 +7071,9 @@
       <c r="I402" s="5"/>
       <c r="J402" s="5"/>
       <c r="K402" s="5"/>
-    </row>
-    <row r="403" spans="1:11">
+      <c r="L402" s="5"/>
+    </row>
+    <row r="403" spans="1:12">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -6693,8 +7085,9 @@
       <c r="I403" s="5"/>
       <c r="J403" s="5"/>
       <c r="K403" s="5"/>
-    </row>
-    <row r="404" spans="1:11">
+      <c r="L403" s="5"/>
+    </row>
+    <row r="404" spans="1:12">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -6706,8 +7099,9 @@
       <c r="I404" s="5"/>
       <c r="J404" s="5"/>
       <c r="K404" s="5"/>
-    </row>
-    <row r="405" spans="1:11">
+      <c r="L404" s="5"/>
+    </row>
+    <row r="405" spans="1:12">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -6719,8 +7113,9 @@
       <c r="I405" s="5"/>
       <c r="J405" s="5"/>
       <c r="K405" s="5"/>
-    </row>
-    <row r="406" spans="1:11">
+      <c r="L405" s="5"/>
+    </row>
+    <row r="406" spans="1:12">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -6732,8 +7127,9 @@
       <c r="I406" s="5"/>
       <c r="J406" s="5"/>
       <c r="K406" s="5"/>
-    </row>
-    <row r="407" spans="1:11">
+      <c r="L406" s="5"/>
+    </row>
+    <row r="407" spans="1:12">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -6745,8 +7141,9 @@
       <c r="I407" s="5"/>
       <c r="J407" s="5"/>
       <c r="K407" s="5"/>
-    </row>
-    <row r="408" spans="1:11">
+      <c r="L407" s="5"/>
+    </row>
+    <row r="408" spans="1:12">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -6758,8 +7155,9 @@
       <c r="I408" s="5"/>
       <c r="J408" s="5"/>
       <c r="K408" s="5"/>
-    </row>
-    <row r="409" spans="1:11">
+      <c r="L408" s="5"/>
+    </row>
+    <row r="409" spans="1:12">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -6771,8 +7169,9 @@
       <c r="I409" s="5"/>
       <c r="J409" s="5"/>
       <c r="K409" s="5"/>
-    </row>
-    <row r="410" spans="1:11">
+      <c r="L409" s="5"/>
+    </row>
+    <row r="410" spans="1:12">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -6784,8 +7183,9 @@
       <c r="I410" s="5"/>
       <c r="J410" s="5"/>
       <c r="K410" s="5"/>
-    </row>
-    <row r="411" spans="1:11">
+      <c r="L410" s="5"/>
+    </row>
+    <row r="411" spans="1:12">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -6797,8 +7197,9 @@
       <c r="I411" s="5"/>
       <c r="J411" s="5"/>
       <c r="K411" s="5"/>
-    </row>
-    <row r="412" spans="1:11">
+      <c r="L411" s="5"/>
+    </row>
+    <row r="412" spans="1:12">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -6810,8 +7211,9 @@
       <c r="I412" s="5"/>
       <c r="J412" s="5"/>
       <c r="K412" s="5"/>
-    </row>
-    <row r="413" spans="1:11">
+      <c r="L412" s="5"/>
+    </row>
+    <row r="413" spans="1:12">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -6823,8 +7225,9 @@
       <c r="I413" s="5"/>
       <c r="J413" s="5"/>
       <c r="K413" s="5"/>
-    </row>
-    <row r="414" spans="1:11">
+      <c r="L413" s="5"/>
+    </row>
+    <row r="414" spans="1:12">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -6836,8 +7239,9 @@
       <c r="I414" s="5"/>
       <c r="J414" s="5"/>
       <c r="K414" s="5"/>
-    </row>
-    <row r="415" spans="1:11">
+      <c r="L414" s="5"/>
+    </row>
+    <row r="415" spans="1:12">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -6849,8 +7253,9 @@
       <c r="I415" s="5"/>
       <c r="J415" s="5"/>
       <c r="K415" s="5"/>
-    </row>
-    <row r="416" spans="1:11">
+      <c r="L415" s="5"/>
+    </row>
+    <row r="416" spans="1:12">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -6862,8 +7267,9 @@
       <c r="I416" s="5"/>
       <c r="J416" s="5"/>
       <c r="K416" s="5"/>
-    </row>
-    <row r="417" spans="1:11">
+      <c r="L416" s="5"/>
+    </row>
+    <row r="417" spans="1:12">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -6875,8 +7281,9 @@
       <c r="I417" s="5"/>
       <c r="J417" s="5"/>
       <c r="K417" s="5"/>
-    </row>
-    <row r="418" spans="1:11">
+      <c r="L417" s="5"/>
+    </row>
+    <row r="418" spans="1:12">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -6888,8 +7295,9 @@
       <c r="I418" s="5"/>
       <c r="J418" s="5"/>
       <c r="K418" s="5"/>
-    </row>
-    <row r="419" spans="1:11">
+      <c r="L418" s="5"/>
+    </row>
+    <row r="419" spans="1:12">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -6901,8 +7309,9 @@
       <c r="I419" s="5"/>
       <c r="J419" s="5"/>
       <c r="K419" s="5"/>
-    </row>
-    <row r="420" spans="1:11">
+      <c r="L419" s="5"/>
+    </row>
+    <row r="420" spans="1:12">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -6914,8 +7323,9 @@
       <c r="I420" s="5"/>
       <c r="J420" s="5"/>
       <c r="K420" s="5"/>
-    </row>
-    <row r="421" spans="1:11">
+      <c r="L420" s="5"/>
+    </row>
+    <row r="421" spans="1:12">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -6927,8 +7337,9 @@
       <c r="I421" s="5"/>
       <c r="J421" s="5"/>
       <c r="K421" s="5"/>
-    </row>
-    <row r="422" spans="1:11">
+      <c r="L421" s="5"/>
+    </row>
+    <row r="422" spans="1:12">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -6940,8 +7351,9 @@
       <c r="I422" s="5"/>
       <c r="J422" s="5"/>
       <c r="K422" s="5"/>
-    </row>
-    <row r="423" spans="1:11">
+      <c r="L422" s="5"/>
+    </row>
+    <row r="423" spans="1:12">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -6953,8 +7365,9 @@
       <c r="I423" s="5"/>
       <c r="J423" s="5"/>
       <c r="K423" s="5"/>
-    </row>
-    <row r="424" spans="1:11">
+      <c r="L423" s="5"/>
+    </row>
+    <row r="424" spans="1:12">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -6966,8 +7379,9 @@
       <c r="I424" s="5"/>
       <c r="J424" s="5"/>
       <c r="K424" s="5"/>
-    </row>
-    <row r="425" spans="1:11">
+      <c r="L424" s="5"/>
+    </row>
+    <row r="425" spans="1:12">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -6979,8 +7393,9 @@
       <c r="I425" s="5"/>
       <c r="J425" s="5"/>
       <c r="K425" s="5"/>
-    </row>
-    <row r="426" spans="1:11">
+      <c r="L425" s="5"/>
+    </row>
+    <row r="426" spans="1:12">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -6992,8 +7407,9 @@
       <c r="I426" s="5"/>
       <c r="J426" s="5"/>
       <c r="K426" s="5"/>
-    </row>
-    <row r="427" spans="1:11">
+      <c r="L426" s="5"/>
+    </row>
+    <row r="427" spans="1:12">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -7005,8 +7421,9 @@
       <c r="I427" s="5"/>
       <c r="J427" s="5"/>
       <c r="K427" s="5"/>
-    </row>
-    <row r="428" spans="1:11">
+      <c r="L427" s="5"/>
+    </row>
+    <row r="428" spans="1:12">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -7018,8 +7435,9 @@
       <c r="I428" s="5"/>
       <c r="J428" s="5"/>
       <c r="K428" s="5"/>
-    </row>
-    <row r="429" spans="1:11">
+      <c r="L428" s="5"/>
+    </row>
+    <row r="429" spans="1:12">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -7031,8 +7449,9 @@
       <c r="I429" s="5"/>
       <c r="J429" s="5"/>
       <c r="K429" s="5"/>
-    </row>
-    <row r="430" spans="1:11">
+      <c r="L429" s="5"/>
+    </row>
+    <row r="430" spans="1:12">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -7044,8 +7463,9 @@
       <c r="I430" s="5"/>
       <c r="J430" s="5"/>
       <c r="K430" s="5"/>
-    </row>
-    <row r="431" spans="1:11">
+      <c r="L430" s="5"/>
+    </row>
+    <row r="431" spans="1:12">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -7057,8 +7477,9 @@
       <c r="I431" s="5"/>
       <c r="J431" s="5"/>
       <c r="K431" s="5"/>
-    </row>
-    <row r="432" spans="1:11">
+      <c r="L431" s="5"/>
+    </row>
+    <row r="432" spans="1:12">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -7070,8 +7491,9 @@
       <c r="I432" s="5"/>
       <c r="J432" s="5"/>
       <c r="K432" s="5"/>
-    </row>
-    <row r="433" spans="1:11">
+      <c r="L432" s="5"/>
+    </row>
+    <row r="433" spans="1:12">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -7083,8 +7505,9 @@
       <c r="I433" s="5"/>
       <c r="J433" s="5"/>
       <c r="K433" s="5"/>
-    </row>
-    <row r="434" spans="1:11">
+      <c r="L433" s="5"/>
+    </row>
+    <row r="434" spans="1:12">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -7096,8 +7519,9 @@
       <c r="I434" s="5"/>
       <c r="J434" s="5"/>
       <c r="K434" s="5"/>
-    </row>
-    <row r="435" spans="1:11">
+      <c r="L434" s="5"/>
+    </row>
+    <row r="435" spans="1:12">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -7109,8 +7533,9 @@
       <c r="I435" s="5"/>
       <c r="J435" s="5"/>
       <c r="K435" s="5"/>
-    </row>
-    <row r="436" spans="1:11">
+      <c r="L435" s="5"/>
+    </row>
+    <row r="436" spans="1:12">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -7122,8 +7547,9 @@
       <c r="I436" s="5"/>
       <c r="J436" s="5"/>
       <c r="K436" s="5"/>
-    </row>
-    <row r="437" spans="1:11">
+      <c r="L436" s="5"/>
+    </row>
+    <row r="437" spans="1:12">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -7135,8 +7561,9 @@
       <c r="I437" s="5"/>
       <c r="J437" s="5"/>
       <c r="K437" s="5"/>
-    </row>
-    <row r="438" spans="1:11">
+      <c r="L437" s="5"/>
+    </row>
+    <row r="438" spans="1:12">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -7148,8 +7575,9 @@
       <c r="I438" s="5"/>
       <c r="J438" s="5"/>
       <c r="K438" s="5"/>
-    </row>
-    <row r="439" spans="1:11">
+      <c r="L438" s="5"/>
+    </row>
+    <row r="439" spans="1:12">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -7161,8 +7589,9 @@
       <c r="I439" s="5"/>
       <c r="J439" s="5"/>
       <c r="K439" s="5"/>
-    </row>
-    <row r="440" spans="1:11">
+      <c r="L439" s="5"/>
+    </row>
+    <row r="440" spans="1:12">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -7174,8 +7603,9 @@
       <c r="I440" s="5"/>
       <c r="J440" s="5"/>
       <c r="K440" s="5"/>
-    </row>
-    <row r="441" spans="1:11">
+      <c r="L440" s="5"/>
+    </row>
+    <row r="441" spans="1:12">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -7187,8 +7617,9 @@
       <c r="I441" s="5"/>
       <c r="J441" s="5"/>
       <c r="K441" s="5"/>
-    </row>
-    <row r="442" spans="1:11">
+      <c r="L441" s="5"/>
+    </row>
+    <row r="442" spans="1:12">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -7200,8 +7631,9 @@
       <c r="I442" s="5"/>
       <c r="J442" s="5"/>
       <c r="K442" s="5"/>
-    </row>
-    <row r="443" spans="1:11">
+      <c r="L442" s="5"/>
+    </row>
+    <row r="443" spans="1:12">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -7213,8 +7645,9 @@
       <c r="I443" s="5"/>
       <c r="J443" s="5"/>
       <c r="K443" s="5"/>
-    </row>
-    <row r="444" spans="1:11">
+      <c r="L443" s="5"/>
+    </row>
+    <row r="444" spans="1:12">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -7226,8 +7659,9 @@
       <c r="I444" s="5"/>
       <c r="J444" s="5"/>
       <c r="K444" s="5"/>
-    </row>
-    <row r="445" spans="1:11">
+      <c r="L444" s="5"/>
+    </row>
+    <row r="445" spans="1:12">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -7239,8 +7673,9 @@
       <c r="I445" s="5"/>
       <c r="J445" s="5"/>
       <c r="K445" s="5"/>
-    </row>
-    <row r="446" spans="1:11">
+      <c r="L445" s="5"/>
+    </row>
+    <row r="446" spans="1:12">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -7252,8 +7687,9 @@
       <c r="I446" s="5"/>
       <c r="J446" s="5"/>
       <c r="K446" s="5"/>
-    </row>
-    <row r="447" spans="1:11">
+      <c r="L446" s="5"/>
+    </row>
+    <row r="447" spans="1:12">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -7265,8 +7701,9 @@
       <c r="I447" s="5"/>
       <c r="J447" s="5"/>
       <c r="K447" s="5"/>
-    </row>
-    <row r="448" spans="1:11">
+      <c r="L447" s="5"/>
+    </row>
+    <row r="448" spans="1:12">
       <c r="A448" s="5"/>
     </row>
     <row r="449" spans="1:1">

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -355,12 +355,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1501,7 +1501,7 @@
         <v>31</v>
       </c>
       <c r="E9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
         <v>4000</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -1432,7 +1432,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I7" s="3">
         <v>75</v>
@@ -1510,7 +1510,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="3">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I9" s="3">
         <v>5</v>
